--- a/Projects/Population Census Data.xlsx
+++ b/Projects/Population Census Data.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Excel\Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01855144-039E-4CC8-8E40-CA19515C9660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B30BC33E-C6CF-42CA-9F76-60CC1FF8BFF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="898" activeTab="3" xr2:uid="{88B5CF03-CC11-4079-967D-347AC28B3826}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="898" xr2:uid="{88B5CF03-CC11-4079-967D-347AC28B3826}"/>
   </bookViews>
   <sheets>
     <sheet name="Population Census Data" sheetId="2" r:id="rId1"/>
     <sheet name="Clients Requirement" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="6" r:id="rId3"/>
+    <sheet name="comparisionsheet" sheetId="6" r:id="rId3"/>
     <sheet name="client soln" sheetId="7" r:id="rId4"/>
     <sheet name="Home Work" sheetId="4" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId6"/>
+    <sheet name="literacyrate" sheetId="5" r:id="rId6"/>
     <sheet name="soln hw" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
@@ -1906,7 +1906,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2053,6 +2053,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2068,13 +2074,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="14">
     <cellStyle name="Comma 2 3" xfId="4" xr:uid="{137E3014-4AA5-4011-A0E3-5376CC52E550}"/>
@@ -2093,6 +2092,23 @@
     <cellStyle name="Normal_Sheet7" xfId="9" xr:uid="{100ABF9F-9F30-44E9-9D50-D2083BAD9301}"/>
   </cellStyles>
   <dxfs count="4">
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2120,23 +2136,6 @@
         </right>
         <top/>
         <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
       </border>
     </dxf>
   </dxfs>
@@ -3169,7 +3168,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="risha" refreshedDate="46120.483737268522" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="468" xr:uid="{083EFD5F-7CCB-47AB-8676-6C72D7B9A5A9}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:D469" sheet="Sheet2"/>
+    <worksheetSource ref="A1:D469" sheet="comparisionsheet"/>
   </cacheSource>
   <cacheFields count="4">
     <cacheField name="Name of Urban Agglomeration/City" numFmtId="0">
@@ -3665,7 +3664,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="risha" refreshedDate="46120.490772106481" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="468" xr:uid="{00278ACE-9FAE-4433-A80E-FF0C1064B213}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:B469" sheet="Sheet1"/>
+    <worksheetSource ref="A1:B469" sheet="literacyrate"/>
   </cacheSource>
   <cacheFields count="2">
     <cacheField name="Name of Urban Agglomeration/City" numFmtId="0">
@@ -12694,13 +12693,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D51BF4A7-71B3-4412-9019-8AB022E3A4FC}" name="Table1" displayName="Table1" ref="A1:D469" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="2" tableBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D51BF4A7-71B3-4412-9019-8AB022E3A4FC}" name="Table1" displayName="Table1" ref="A1:D469" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="2" tableBorderDxfId="1">
   <autoFilter ref="A1:D469" xr:uid="{D51BF4A7-71B3-4412-9019-8AB022E3A4FC}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{50930E3F-11B0-4BB1-9768-695DC00D0965}" name="Name of Urban Agglomeration/City"/>
     <tableColumn id="2" xr3:uid="{E53A8C94-255E-4E82-90A1-D8353B62595B}" name="Population Males"/>
     <tableColumn id="3" xr3:uid="{98B2C8D7-1A28-4592-8C57-0970B156B582}" name="Population Females"/>
-    <tableColumn id="4" xr3:uid="{C0FED487-D670-4DEB-9BC2-185C39B1A9B4}" name="Calculated Sex Ratio" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{C0FED487-D670-4DEB-9BC2-185C39B1A9B4}" name="Calculated Sex Ratio" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -39845,33 +39844,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="54" t="s">
         <v>487</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
     </row>
     <row r="2" spans="1:9" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I2" s="46"/>
     </row>
     <row r="3" spans="1:9" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="55" t="s">
         <v>488</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="55"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="57"/>
     </row>
     <row r="4" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="I4" s="46"/>
@@ -39923,16 +39922,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="57" t="s">
+      <c r="C1" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="58" t="s">
+      <c r="D1" s="53" t="s">
         <v>491</v>
       </c>
     </row>
@@ -46525,10 +46524,10 @@
       <c r="A4" s="51" t="s">
         <v>440</v>
       </c>
-      <c r="B4" s="59">
+      <c r="B4">
         <v>757769</v>
       </c>
-      <c r="C4" s="59">
+      <c r="C4">
         <v>885123</v>
       </c>
       <c r="D4" s="49">
@@ -46539,10 +46538,10 @@
       <c r="A5" s="51" t="s">
         <v>443</v>
       </c>
-      <c r="B5" s="59">
+      <c r="B5">
         <v>197960</v>
       </c>
-      <c r="C5" s="59">
+      <c r="C5">
         <v>229131</v>
       </c>
       <c r="D5" s="49">
@@ -46553,10 +46552,10 @@
       <c r="A6" s="51" t="s">
         <v>448</v>
       </c>
-      <c r="B6" s="59">
+      <c r="B6">
         <v>106983</v>
       </c>
-      <c r="C6" s="59">
+      <c r="C6">
         <v>122723</v>
       </c>
       <c r="D6" s="49">
@@ -46567,10 +46566,10 @@
       <c r="A7" s="51" t="s">
         <v>437</v>
       </c>
-      <c r="B7" s="59">
+      <c r="B7">
         <v>876049</v>
       </c>
-      <c r="C7" s="59">
+      <c r="C7">
         <v>978734</v>
       </c>
       <c r="D7" s="49">
@@ -46581,10 +46580,10 @@
       <c r="A8" s="51" t="s">
         <v>436</v>
       </c>
-      <c r="B8" s="59">
+      <c r="B8">
         <v>966138</v>
       </c>
-      <c r="C8" s="59">
+      <c r="C8">
         <v>1064381</v>
       </c>
       <c r="D8" s="49">
@@ -46595,10 +46594,10 @@
       <c r="A9" s="51" t="s">
         <v>438</v>
       </c>
-      <c r="B9" s="59">
+      <c r="B9">
         <v>809154</v>
       </c>
-      <c r="C9" s="59">
+      <c r="C9">
         <v>889491</v>
       </c>
       <c r="D9" s="49">
@@ -46609,10 +46608,10 @@
       <c r="A10" s="51" t="s">
         <v>441</v>
       </c>
-      <c r="B10" s="59">
+      <c r="B10">
         <v>529838</v>
       </c>
-      <c r="C10" s="59">
+      <c r="C10">
         <v>580167</v>
       </c>
       <c r="D10" s="49">
@@ -46623,10 +46622,10 @@
       <c r="A11" s="51" t="s">
         <v>447</v>
       </c>
-      <c r="B11" s="59">
+      <c r="B11">
         <v>114183</v>
       </c>
-      <c r="C11" s="59">
+      <c r="C11">
         <v>124055</v>
       </c>
       <c r="D11" s="49">
@@ -46637,10 +46636,10 @@
       <c r="A12" s="51" t="s">
         <v>451</v>
       </c>
-      <c r="B12" s="59">
+      <c r="B12">
         <v>55276</v>
       </c>
-      <c r="C12" s="59">
+      <c r="C12">
         <v>59625</v>
       </c>
       <c r="D12" s="49">
@@ -46651,10 +46650,10 @@
       <c r="A13" s="51" t="s">
         <v>449</v>
       </c>
-      <c r="B13" s="59">
+      <c r="B13">
         <v>92960</v>
       </c>
-      <c r="C13" s="59">
+      <c r="C13">
         <v>99801</v>
       </c>
       <c r="D13" s="49">
@@ -46665,10 +46664,10 @@
       <c r="A14" s="51" t="s">
         <v>450</v>
       </c>
-      <c r="B14" s="59">
+      <c r="B14">
         <v>61740</v>
       </c>
-      <c r="C14" s="59">
+      <c r="C14">
         <v>66231</v>
       </c>
       <c r="D14" s="49">
@@ -46679,10 +46678,10 @@
       <c r="A15" s="51" t="s">
         <v>446</v>
       </c>
-      <c r="B15" s="59">
+      <c r="B15">
         <v>116401</v>
       </c>
-      <c r="C15" s="59">
+      <c r="C15">
         <v>124671</v>
       </c>
       <c r="D15" s="49">
@@ -46693,10 +46692,10 @@
       <c r="A16" s="51" t="s">
         <v>439</v>
       </c>
-      <c r="B16" s="59">
+      <c r="B16">
         <v>815200</v>
       </c>
-      <c r="C16" s="59">
+      <c r="C16">
         <v>872206</v>
       </c>
       <c r="D16" s="49">
@@ -46707,10 +46706,10 @@
       <c r="A17" s="51" t="s">
         <v>191</v>
       </c>
-      <c r="B17" s="59">
+      <c r="B17">
         <v>201635</v>
       </c>
-      <c r="C17" s="59">
+      <c r="C17">
         <v>212653</v>
       </c>
       <c r="D17" s="49">
@@ -46721,10 +46720,10 @@
       <c r="A18" s="51" t="s">
         <v>444</v>
       </c>
-      <c r="B18" s="59">
+      <c r="B18">
         <v>174465</v>
       </c>
-      <c r="C18" s="59">
+      <c r="C18">
         <v>183068</v>
       </c>
       <c r="D18" s="49">
@@ -46735,10 +46734,10 @@
       <c r="A19" s="51" t="s">
         <v>442</v>
       </c>
-      <c r="B19" s="59">
+      <c r="B19">
         <v>222398</v>
       </c>
-      <c r="C19" s="59">
+      <c r="C19">
         <v>233010</v>
       </c>
       <c r="D19" s="49">
@@ -46749,10 +46748,10 @@
       <c r="A20" s="51" t="s">
         <v>445</v>
       </c>
-      <c r="B20" s="59">
+      <c r="B20">
         <v>143650</v>
       </c>
-      <c r="C20" s="59">
+      <c r="C20">
         <v>149916</v>
       </c>
       <c r="D20" s="49">
@@ -46763,10 +46762,10 @@
       <c r="A21" s="51" t="s">
         <v>377</v>
       </c>
-      <c r="B21" s="59">
+      <c r="B21">
         <v>117412</v>
       </c>
-      <c r="C21" s="59">
+      <c r="C21">
         <v>121962</v>
       </c>
       <c r="D21" s="49">
@@ -46777,10 +46776,10 @@
       <c r="A22" s="51" t="s">
         <v>470</v>
       </c>
-      <c r="B22" s="59">
+      <c r="B22">
         <v>110132</v>
       </c>
-      <c r="C22" s="59">
+      <c r="C22">
         <v>114197</v>
       </c>
       <c r="D22" s="49">
@@ -46791,10 +46790,10 @@
       <c r="A23" s="51" t="s">
         <v>396</v>
       </c>
-      <c r="B23" s="59">
+      <c r="B23">
         <v>58652</v>
       </c>
-      <c r="C23" s="59">
+      <c r="C23">
         <v>60798</v>
       </c>
       <c r="D23" s="49">
@@ -46805,10 +46804,10 @@
       <c r="A24" s="51" t="s">
         <v>464</v>
       </c>
-      <c r="B24" s="59">
+      <c r="B24">
         <v>142765</v>
       </c>
-      <c r="C24" s="59">
+      <c r="C24">
         <v>147959</v>
       </c>
       <c r="D24" s="49">
@@ -46819,10 +46818,10 @@
       <c r="A25" s="51" t="s">
         <v>369</v>
       </c>
-      <c r="B25" s="59">
+      <c r="B25">
         <v>217573</v>
       </c>
-      <c r="C25" s="59">
+      <c r="C25">
         <v>225363</v>
       </c>
       <c r="D25" s="49">
@@ -46833,10 +46832,10 @@
       <c r="A26" s="51" t="s">
         <v>385</v>
       </c>
-      <c r="B26" s="59">
+      <c r="B26">
         <v>83561</v>
       </c>
-      <c r="C26" s="59">
+      <c r="C26">
         <v>86447</v>
       </c>
       <c r="D26" s="49">
@@ -46847,10 +46846,10 @@
       <c r="A27" s="51" t="s">
         <v>485</v>
       </c>
-      <c r="B27" s="59">
+      <c r="B27">
         <v>321834</v>
       </c>
-      <c r="C27" s="59">
+      <c r="C27">
         <v>332558</v>
       </c>
       <c r="D27" s="49">
@@ -46861,10 +46860,10 @@
       <c r="A28" s="51" t="s">
         <v>483</v>
       </c>
-      <c r="B28" s="59">
+      <c r="B28">
         <v>56052</v>
       </c>
-      <c r="C28" s="59">
+      <c r="C28">
         <v>57804</v>
       </c>
       <c r="D28" s="49">
@@ -46875,10 +46874,10 @@
       <c r="A29" s="51" t="s">
         <v>435</v>
       </c>
-      <c r="B29" s="59">
+      <c r="B29">
         <v>1042809</v>
       </c>
-      <c r="C29" s="59">
+      <c r="C29">
         <v>1075181</v>
       </c>
       <c r="D29" s="49">
@@ -46889,10 +46888,10 @@
       <c r="A30" s="51" t="s">
         <v>391</v>
       </c>
-      <c r="B30" s="59">
+      <c r="B30">
         <v>72457</v>
       </c>
-      <c r="C30" s="59">
+      <c r="C30">
         <v>74599</v>
       </c>
       <c r="D30" s="49">
@@ -46903,10 +46902,10 @@
       <c r="A31" s="51" t="s">
         <v>192</v>
       </c>
-      <c r="B31" s="59">
+      <c r="B31">
         <v>143803</v>
       </c>
-      <c r="C31" s="59">
+      <c r="C31">
         <v>148019</v>
       </c>
       <c r="D31" s="49">
@@ -46917,10 +46916,10 @@
       <c r="A32" s="51" t="s">
         <v>388</v>
       </c>
-      <c r="B32" s="59">
+      <c r="B32">
         <v>80215</v>
       </c>
-      <c r="C32" s="59">
+      <c r="C32">
         <v>82510</v>
       </c>
       <c r="D32" s="49">
@@ -46931,10 +46930,10 @@
       <c r="A33" s="51" t="s">
         <v>376</v>
       </c>
-      <c r="B33" s="59">
+      <c r="B33">
         <v>123747</v>
       </c>
-      <c r="C33" s="59">
+      <c r="C33">
         <v>126946</v>
       </c>
       <c r="D33" s="49">
@@ -46945,10 +46944,10 @@
       <c r="A34" s="51" t="s">
         <v>475</v>
       </c>
-      <c r="B34" s="59">
+      <c r="B34">
         <v>85593</v>
       </c>
-      <c r="C34" s="59">
+      <c r="C34">
         <v>87768</v>
       </c>
       <c r="D34" s="49">
@@ -46959,10 +46958,10 @@
       <c r="A35" s="51" t="s">
         <v>386</v>
       </c>
-      <c r="B35" s="59">
+      <c r="B35">
         <v>81324</v>
       </c>
-      <c r="C35" s="59">
+      <c r="C35">
         <v>83325</v>
       </c>
       <c r="D35" s="49">
@@ -46973,10 +46972,10 @@
       <c r="A36" s="51" t="s">
         <v>468</v>
       </c>
-      <c r="B36" s="59">
+      <c r="B36">
         <v>115294</v>
       </c>
-      <c r="C36" s="59">
+      <c r="C36">
         <v>118080</v>
       </c>
       <c r="D36" s="49">
@@ -46987,10 +46986,10 @@
       <c r="A37" s="51" t="s">
         <v>404</v>
       </c>
-      <c r="B37" s="59">
+      <c r="B37">
         <v>51236</v>
       </c>
-      <c r="C37" s="59">
+      <c r="C37">
         <v>52467</v>
       </c>
       <c r="D37" s="49">
@@ -47001,10 +47000,10 @@
       <c r="A38" s="51" t="s">
         <v>484</v>
       </c>
-      <c r="B38" s="59">
+      <c r="B38">
         <v>50809</v>
       </c>
-      <c r="C38" s="59">
+      <c r="C38">
         <v>52029</v>
       </c>
       <c r="D38" s="49">
@@ -47015,10 +47014,10 @@
       <c r="A39" s="51" t="s">
         <v>405</v>
       </c>
-      <c r="B39" s="59">
+      <c r="B39">
         <v>50201</v>
       </c>
-      <c r="C39" s="59">
+      <c r="C39">
         <v>51349</v>
       </c>
       <c r="D39" s="49">
@@ -47029,10 +47028,10 @@
       <c r="A40" s="51" t="s">
         <v>460</v>
       </c>
-      <c r="B40" s="59">
+      <c r="B40">
         <v>246710</v>
       </c>
-      <c r="C40" s="59">
+      <c r="C40">
         <v>252274</v>
       </c>
       <c r="D40" s="49">
@@ -47043,10 +47042,10 @@
       <c r="A41" s="51" t="s">
         <v>366</v>
       </c>
-      <c r="B41" s="59">
+      <c r="B41">
         <v>236489</v>
       </c>
-      <c r="C41" s="59">
+      <c r="C41">
         <v>241710</v>
       </c>
       <c r="D41" s="49">
@@ -47057,10 +47056,10 @@
       <c r="A42" s="51" t="s">
         <v>482</v>
       </c>
-      <c r="B42" s="59">
+      <c r="B42">
         <v>57746</v>
       </c>
-      <c r="C42" s="59">
+      <c r="C42">
         <v>58966</v>
       </c>
       <c r="D42" s="49">
@@ -47071,10 +47070,10 @@
       <c r="A43" s="51" t="s">
         <v>465</v>
       </c>
-      <c r="B43" s="59">
+      <c r="B43">
         <v>129884</v>
       </c>
-      <c r="C43" s="59">
+      <c r="C43">
         <v>132462</v>
       </c>
       <c r="D43" s="49">
@@ -47085,10 +47084,10 @@
       <c r="A44" s="51" t="s">
         <v>422</v>
       </c>
-      <c r="B44" s="59">
+      <c r="B44">
         <v>81927</v>
       </c>
-      <c r="C44" s="59">
+      <c r="C44">
         <v>83536</v>
       </c>
       <c r="D44" s="49">
@@ -47099,10 +47098,10 @@
       <c r="A45" s="51" t="s">
         <v>452</v>
       </c>
-      <c r="B45" s="59">
+      <c r="B45">
         <v>56753</v>
       </c>
-      <c r="C45" s="59">
+      <c r="C45">
         <v>57821</v>
       </c>
       <c r="D45" s="49">
@@ -47113,10 +47112,10 @@
       <c r="A46" s="51" t="s">
         <v>374</v>
       </c>
-      <c r="B46" s="59">
+      <c r="B46">
         <v>129937</v>
       </c>
-      <c r="C46" s="59">
+      <c r="C46">
         <v>132372</v>
       </c>
       <c r="D46" s="49">
@@ -47127,10 +47126,10 @@
       <c r="A47" s="51" t="s">
         <v>480</v>
       </c>
-      <c r="B47" s="59">
+      <c r="B47">
         <v>61564</v>
       </c>
-      <c r="C47" s="59">
+      <c r="C47">
         <v>62710</v>
       </c>
       <c r="D47" s="49">
@@ -47141,10 +47140,10 @@
       <c r="A48" s="51" t="s">
         <v>423</v>
       </c>
-      <c r="B48" s="59">
+      <c r="B48">
         <v>81940</v>
       </c>
-      <c r="C48" s="59">
+      <c r="C48">
         <v>83461</v>
       </c>
       <c r="D48" s="49">
@@ -47155,10 +47154,10 @@
       <c r="A49" s="51" t="s">
         <v>364</v>
       </c>
-      <c r="B49" s="59">
+      <c r="B49">
         <v>333894</v>
       </c>
-      <c r="C49" s="59">
+      <c r="C49">
         <v>340058</v>
       </c>
       <c r="D49" s="49">
@@ -47169,10 +47168,10 @@
       <c r="A50" s="51" t="s">
         <v>401</v>
       </c>
-      <c r="B50" s="59">
+      <c r="B50">
         <v>52800</v>
       </c>
-      <c r="C50" s="59">
+      <c r="C50">
         <v>53724</v>
       </c>
       <c r="D50" s="49">
@@ -47183,10 +47182,10 @@
       <c r="A51" s="51" t="s">
         <v>394</v>
       </c>
-      <c r="B51" s="59">
+      <c r="B51">
         <v>62695</v>
       </c>
-      <c r="C51" s="59">
+      <c r="C51">
         <v>63784</v>
       </c>
       <c r="D51" s="49">
@@ -47197,10 +47196,10 @@
       <c r="A52" s="51" t="s">
         <v>476</v>
       </c>
-      <c r="B52" s="59">
+      <c r="B52">
         <v>82844</v>
       </c>
-      <c r="C52" s="59">
+      <c r="C52">
         <v>84254</v>
       </c>
       <c r="D52" s="49">
@@ -47211,10 +47210,10 @@
       <c r="A53" s="51" t="s">
         <v>456</v>
       </c>
-      <c r="B53" s="59">
+      <c r="B53">
         <v>507180</v>
       </c>
-      <c r="C53" s="59">
+      <c r="C53">
         <v>514537</v>
       </c>
       <c r="D53" s="49">
@@ -47225,10 +47224,10 @@
       <c r="A54" s="51" t="s">
         <v>409</v>
       </c>
-      <c r="B54" s="59">
+      <c r="B54">
         <v>307624</v>
       </c>
-      <c r="C54" s="59">
+      <c r="C54">
         <v>312040</v>
       </c>
       <c r="D54" s="49">
@@ -47239,10 +47238,10 @@
       <c r="A55" s="51" t="s">
         <v>479</v>
       </c>
-      <c r="B55" s="59">
+      <c r="B55">
         <v>64624</v>
       </c>
-      <c r="C55" s="59">
+      <c r="C55">
         <v>65495</v>
       </c>
       <c r="D55" s="49">
@@ -47253,10 +47252,10 @@
       <c r="A56" s="51" t="s">
         <v>428</v>
       </c>
-      <c r="B56" s="59">
+      <c r="B56">
         <v>58859</v>
       </c>
-      <c r="C56" s="59">
+      <c r="C56">
         <v>59637</v>
       </c>
       <c r="D56" s="49">
@@ -47267,10 +47266,10 @@
       <c r="A57" s="51" t="s">
         <v>399</v>
       </c>
-      <c r="B57" s="59">
+      <c r="B57">
         <v>56600</v>
       </c>
-      <c r="C57" s="59">
+      <c r="C57">
         <v>57293</v>
       </c>
       <c r="D57" s="49">
@@ -47281,10 +47280,10 @@
       <c r="A58" s="51" t="s">
         <v>392</v>
       </c>
-      <c r="B58" s="59">
+      <c r="B58">
         <v>73077</v>
       </c>
-      <c r="C58" s="59">
+      <c r="C58">
         <v>73911</v>
       </c>
       <c r="D58" s="49">
@@ -47295,10 +47294,10 @@
       <c r="A59" s="51" t="s">
         <v>478</v>
       </c>
-      <c r="B59" s="59">
+      <c r="B59">
         <v>67260</v>
       </c>
-      <c r="C59" s="59">
+      <c r="C59">
         <v>67975</v>
       </c>
       <c r="D59" s="49">
@@ -47309,10 +47308,10 @@
       <c r="A60" s="51" t="s">
         <v>461</v>
       </c>
-      <c r="B60" s="59">
+      <c r="B60">
         <v>239735</v>
       </c>
-      <c r="C60" s="59">
+      <c r="C60">
         <v>242231</v>
       </c>
       <c r="D60" s="49">
@@ -47323,10 +47322,10 @@
       <c r="A61" s="51" t="s">
         <v>424</v>
       </c>
-      <c r="B61" s="59">
+      <c r="B61">
         <v>75020</v>
       </c>
-      <c r="C61" s="59">
+      <c r="C61">
         <v>75756</v>
       </c>
       <c r="D61" s="49">
@@ -47337,10 +47336,10 @@
       <c r="A62" s="51" t="s">
         <v>463</v>
       </c>
-      <c r="B62" s="59">
+      <c r="B62">
         <v>145438</v>
       </c>
-      <c r="C62" s="59">
+      <c r="C62">
         <v>146694</v>
       </c>
       <c r="D62" s="49">
@@ -47351,10 +47350,10 @@
       <c r="A63" s="51" t="s">
         <v>382</v>
       </c>
-      <c r="B63" s="59">
+      <c r="B63">
         <v>92006</v>
       </c>
-      <c r="C63" s="59">
+      <c r="C63">
         <v>92765</v>
       </c>
       <c r="D63" s="49">
@@ -47365,10 +47364,10 @@
       <c r="A64" s="51" t="s">
         <v>466</v>
       </c>
-      <c r="B64" s="59">
+      <c r="B64">
         <v>116869</v>
       </c>
-      <c r="C64" s="59">
+      <c r="C64">
         <v>117819</v>
       </c>
       <c r="D64" s="49">
@@ -47379,10 +47378,10 @@
       <c r="A65" s="51" t="s">
         <v>384</v>
       </c>
-      <c r="B65" s="59">
+      <c r="B65">
         <v>87480</v>
       </c>
-      <c r="C65" s="59">
+      <c r="C65">
         <v>88160</v>
       </c>
       <c r="D65" s="49">
@@ -47393,10 +47392,10 @@
       <c r="A66" s="51" t="s">
         <v>397</v>
       </c>
-      <c r="B66" s="59">
+      <c r="B66">
         <v>58941</v>
       </c>
-      <c r="C66" s="59">
+      <c r="C66">
         <v>59348</v>
       </c>
       <c r="D66" s="49">
@@ -47407,10 +47406,10 @@
       <c r="A67" s="51" t="s">
         <v>194</v>
       </c>
-      <c r="B67" s="59">
+      <c r="B67">
         <v>176591</v>
       </c>
-      <c r="C67" s="59">
+      <c r="C67">
         <v>177734</v>
       </c>
       <c r="D67" s="49">
@@ -47421,10 +47420,10 @@
       <c r="A68" s="51" t="s">
         <v>403</v>
       </c>
-      <c r="B68" s="59">
+      <c r="B68">
         <v>51819</v>
       </c>
-      <c r="C68" s="59">
+      <c r="C68">
         <v>52143</v>
       </c>
       <c r="D68" s="49">
@@ -47435,10 +47434,10 @@
       <c r="A69" s="51" t="s">
         <v>213</v>
       </c>
-      <c r="B69" s="59">
+      <c r="B69">
         <v>119151</v>
       </c>
-      <c r="C69" s="59">
+      <c r="C69">
         <v>119871</v>
       </c>
       <c r="D69" s="49">
@@ -47449,10 +47448,10 @@
       <c r="A70" s="51" t="s">
         <v>467</v>
       </c>
-      <c r="B70" s="59">
+      <c r="B70">
         <v>116536</v>
       </c>
-      <c r="C70" s="59">
+      <c r="C70">
         <v>117227</v>
       </c>
       <c r="D70" s="49">
@@ -47463,10 +47462,10 @@
       <c r="A71" s="51" t="s">
         <v>421</v>
       </c>
-      <c r="B71" s="59">
+      <c r="B71">
         <v>86165</v>
       </c>
-      <c r="C71" s="59">
+      <c r="C71">
         <v>86648</v>
       </c>
       <c r="D71" s="49">
@@ -47477,10 +47476,10 @@
       <c r="A72" s="51" t="s">
         <v>420</v>
       </c>
-      <c r="B72" s="59">
+      <c r="B72">
         <v>86335</v>
       </c>
-      <c r="C72" s="59">
+      <c r="C72">
         <v>86799</v>
       </c>
       <c r="D72" s="49">
@@ -47491,10 +47490,10 @@
       <c r="A73" s="51" t="s">
         <v>225</v>
       </c>
-      <c r="B73" s="59">
+      <c r="B73">
         <v>65839</v>
       </c>
-      <c r="C73" s="59">
+      <c r="C73">
         <v>66177</v>
       </c>
       <c r="D73" s="49">
@@ -47505,10 +47504,10 @@
       <c r="A74" s="51" t="s">
         <v>473</v>
       </c>
-      <c r="B74" s="59">
+      <c r="B74">
         <v>90502</v>
       </c>
-      <c r="C74" s="59">
+      <c r="C74">
         <v>90845</v>
       </c>
       <c r="D74" s="49">
@@ -47519,10 +47518,10 @@
       <c r="A75" s="51" t="s">
         <v>400</v>
       </c>
-      <c r="B75" s="59">
+      <c r="B75">
         <v>54027</v>
       </c>
-      <c r="C75" s="59">
+      <c r="C75">
         <v>54222</v>
       </c>
       <c r="D75" s="49">
@@ -47533,10 +47532,10 @@
       <c r="A76" s="51" t="s">
         <v>427</v>
       </c>
-      <c r="B76" s="59">
+      <c r="B76">
         <v>68748</v>
       </c>
-      <c r="C76" s="59">
+      <c r="C76">
         <v>68987</v>
       </c>
       <c r="D76" s="49">
@@ -47547,10 +47546,10 @@
       <c r="A77" s="51" t="s">
         <v>419</v>
       </c>
-      <c r="B77" s="59">
+      <c r="B77">
         <v>102923</v>
       </c>
-      <c r="C77" s="59">
+      <c r="C77">
         <v>103236</v>
       </c>
       <c r="D77" s="49">
@@ -47561,10 +47560,10 @@
       <c r="A78" s="51" t="s">
         <v>193</v>
       </c>
-      <c r="B78" s="59">
+      <c r="B78">
         <v>199616</v>
       </c>
-      <c r="C78" s="59">
+      <c r="C78">
         <v>200072</v>
       </c>
       <c r="D78" s="49">
@@ -47575,10 +47574,10 @@
       <c r="A79" s="51" t="s">
         <v>259</v>
       </c>
-      <c r="B79" s="59">
+      <c r="B79">
         <v>50769</v>
       </c>
-      <c r="C79" s="59">
+      <c r="C79">
         <v>50876</v>
       </c>
       <c r="D79" s="49">
@@ -47589,10 +47588,10 @@
       <c r="A80" s="51" t="s">
         <v>471</v>
       </c>
-      <c r="B80" s="59">
+      <c r="B80">
         <v>110800</v>
       </c>
-      <c r="C80" s="59">
+      <c r="C80">
         <v>110949</v>
       </c>
       <c r="D80" s="49">
@@ -47603,10 +47602,10 @@
       <c r="A81" s="51" t="s">
         <v>372</v>
       </c>
-      <c r="B81" s="59">
+      <c r="B81">
         <v>155163</v>
       </c>
-      <c r="C81" s="59">
+      <c r="C81">
         <v>155304</v>
       </c>
       <c r="D81" s="49">
@@ -47617,10 +47616,10 @@
       <c r="A82" s="51" t="s">
         <v>481</v>
       </c>
-      <c r="B82" s="59">
+      <c r="B82">
         <v>58601</v>
       </c>
-      <c r="C82" s="59">
+      <c r="C82">
         <v>58614</v>
       </c>
       <c r="D82" s="49">
@@ -47631,10 +47630,10 @@
       <c r="A83" s="51" t="s">
         <v>429</v>
       </c>
-      <c r="B83" s="59">
+      <c r="B83">
         <v>57228</v>
       </c>
-      <c r="C83" s="59">
+      <c r="C83">
         <v>57231</v>
       </c>
       <c r="D83" s="49">
@@ -47645,10 +47644,10 @@
       <c r="A84" s="51" t="s">
         <v>477</v>
       </c>
-      <c r="B84" s="59">
+      <c r="B84">
         <v>72351</v>
       </c>
-      <c r="C84" s="59">
+      <c r="C84">
         <v>72332</v>
       </c>
       <c r="D84" s="49">
@@ -47659,10 +47658,10 @@
       <c r="A85" s="51" t="s">
         <v>378</v>
       </c>
-      <c r="B85" s="59">
+      <c r="B85">
         <v>108986</v>
       </c>
-      <c r="C85" s="59">
+      <c r="C85">
         <v>108909</v>
       </c>
       <c r="D85" s="49">
@@ -47673,10 +47672,10 @@
       <c r="A86" s="51" t="s">
         <v>462</v>
       </c>
-      <c r="B86" s="59">
+      <c r="B86">
         <v>205459</v>
       </c>
-      <c r="C86" s="59">
+      <c r="C86">
         <v>205301</v>
       </c>
       <c r="D86" s="49">
@@ -47687,10 +47686,10 @@
       <c r="A87" s="51" t="s">
         <v>383</v>
       </c>
-      <c r="B87" s="59">
+      <c r="B87">
         <v>89692</v>
       </c>
-      <c r="C87" s="59">
+      <c r="C87">
         <v>89575</v>
       </c>
       <c r="D87" s="49">
@@ -47701,10 +47700,10 @@
       <c r="A88" s="51" t="s">
         <v>379</v>
       </c>
-      <c r="B88" s="59">
+      <c r="B88">
         <v>106034</v>
       </c>
-      <c r="C88" s="59">
+      <c r="C88">
         <v>105753</v>
       </c>
       <c r="D88" s="49">
@@ -47715,10 +47714,10 @@
       <c r="A89" s="51" t="s">
         <v>367</v>
       </c>
-      <c r="B89" s="59">
+      <c r="B89">
         <v>239401</v>
       </c>
-      <c r="C89" s="59">
+      <c r="C89">
         <v>238723</v>
       </c>
       <c r="D89" s="49">
@@ -47729,10 +47728,10 @@
       <c r="A90" s="51" t="s">
         <v>454</v>
       </c>
-      <c r="B90" s="59">
+      <c r="B90">
         <v>1077812</v>
       </c>
-      <c r="C90" s="59">
+      <c r="C90">
         <v>1073654</v>
       </c>
       <c r="D90" s="49">
@@ -47743,10 +47742,10 @@
       <c r="A91" s="51" t="s">
         <v>221</v>
       </c>
-      <c r="B91" s="59">
+      <c r="B91">
         <v>82466</v>
       </c>
-      <c r="C91" s="59">
+      <c r="C91">
         <v>82127</v>
       </c>
       <c r="D91" s="49">
@@ -47757,10 +47756,10 @@
       <c r="A92" s="51" t="s">
         <v>459</v>
       </c>
-      <c r="B92" s="59">
+      <c r="B92">
         <v>261470</v>
       </c>
-      <c r="C92" s="59">
+      <c r="C92">
         <v>260306</v>
       </c>
       <c r="D92" s="49">
@@ -47771,10 +47770,10 @@
       <c r="A93" s="51" t="s">
         <v>455</v>
       </c>
-      <c r="B93" s="59">
+      <c r="B93">
         <v>732861</v>
       </c>
-      <c r="C93" s="59">
+      <c r="C93">
         <v>729559</v>
       </c>
       <c r="D93" s="49">
@@ -47785,10 +47784,10 @@
       <c r="A94" s="51" t="s">
         <v>402</v>
       </c>
-      <c r="B94" s="59">
+      <c r="B94">
         <v>52610</v>
       </c>
-      <c r="C94" s="59">
+      <c r="C94">
         <v>52346</v>
       </c>
       <c r="D94" s="49">
@@ -47799,10 +47798,10 @@
       <c r="A95" s="51" t="s">
         <v>363</v>
       </c>
-      <c r="B95" s="59">
+      <c r="B95">
         <v>380833</v>
       </c>
-      <c r="C95" s="59">
+      <c r="C95">
         <v>378761</v>
       </c>
       <c r="D95" s="49">
@@ -47813,10 +47812,10 @@
       <c r="A96" s="51" t="s">
         <v>389</v>
       </c>
-      <c r="B96" s="59">
+      <c r="B96">
         <v>77088</v>
       </c>
-      <c r="C96" s="59">
+      <c r="C96">
         <v>76648</v>
       </c>
       <c r="D96" s="49">
@@ -47827,10 +47826,10 @@
       <c r="A97" s="51" t="s">
         <v>381</v>
       </c>
-      <c r="B97" s="59">
+      <c r="B97">
         <v>103541</v>
       </c>
-      <c r="C97" s="59">
+      <c r="C97">
         <v>102878</v>
       </c>
       <c r="D97" s="49">
@@ -47841,10 +47840,10 @@
       <c r="A98" s="51" t="s">
         <v>407</v>
       </c>
-      <c r="B98" s="59">
+      <c r="B98">
         <v>493692</v>
       </c>
-      <c r="C98" s="59">
+      <c r="C98">
         <v>490201</v>
       </c>
       <c r="D98" s="49">
@@ -47855,10 +47854,10 @@
       <c r="A99" s="51" t="s">
         <v>255</v>
       </c>
-      <c r="B99" s="59">
+      <c r="B99">
         <v>81873</v>
       </c>
-      <c r="C99" s="59">
+      <c r="C99">
         <v>81249</v>
       </c>
       <c r="D99" s="49">
@@ -47869,10 +47868,10 @@
       <c r="A100" s="51" t="s">
         <v>352</v>
       </c>
-      <c r="B100" s="59">
+      <c r="B100">
         <v>66756</v>
       </c>
-      <c r="C100" s="59">
+      <c r="C100">
         <v>66133</v>
       </c>
       <c r="D100" s="49">
@@ -47883,10 +47882,10 @@
       <c r="A101" s="51" t="s">
         <v>415</v>
       </c>
-      <c r="B101" s="59">
+      <c r="B101">
         <v>161978</v>
       </c>
-      <c r="C101" s="59">
+      <c r="C101">
         <v>160450</v>
       </c>
       <c r="D101" s="49">
@@ -47897,10 +47896,10 @@
       <c r="A102" s="51" t="s">
         <v>243</v>
       </c>
-      <c r="B102" s="59">
+      <c r="B102">
         <v>331246</v>
       </c>
-      <c r="C102" s="59">
+      <c r="C102">
         <v>327740</v>
       </c>
       <c r="D102" s="49">
@@ -47911,10 +47910,10 @@
       <c r="A103" s="51" t="s">
         <v>370</v>
       </c>
-      <c r="B103" s="59">
+      <c r="B103">
         <v>172969</v>
       </c>
-      <c r="C103" s="59">
+      <c r="C103">
         <v>171109</v>
       </c>
       <c r="D103" s="49">
@@ -47925,10 +47924,10 @@
       <c r="A104" s="51" t="s">
         <v>425</v>
       </c>
-      <c r="B104" s="59">
+      <c r="B104">
         <v>73193</v>
       </c>
-      <c r="C104" s="59">
+      <c r="C104">
         <v>72387</v>
       </c>
       <c r="D104" s="49">
@@ -47939,10 +47938,10 @@
       <c r="A105" s="51" t="s">
         <v>413</v>
       </c>
-      <c r="B105" s="59">
+      <c r="B105">
         <v>206026</v>
       </c>
-      <c r="C105" s="59">
+      <c r="C105">
         <v>203618</v>
       </c>
       <c r="D105" s="49">
@@ -47953,10 +47952,10 @@
       <c r="A106" s="51" t="s">
         <v>368</v>
       </c>
-      <c r="B106" s="59">
+      <c r="B106">
         <v>231456</v>
       </c>
-      <c r="C106" s="59">
+      <c r="C106">
         <v>228529</v>
       </c>
       <c r="D106" s="49">
@@ -47967,10 +47966,10 @@
       <c r="A107" s="51" t="s">
         <v>362</v>
       </c>
-      <c r="B107" s="59">
+      <c r="B107">
         <v>750770</v>
       </c>
-      <c r="C107" s="59">
+      <c r="C107">
         <v>740432</v>
       </c>
       <c r="D107" s="49">
@@ -47981,10 +47980,10 @@
       <c r="A108" s="51" t="s">
         <v>230</v>
       </c>
-      <c r="B108" s="59">
+      <c r="B108">
         <v>53803</v>
       </c>
-      <c r="C108" s="59">
+      <c r="C108">
         <v>52957</v>
       </c>
       <c r="D108" s="49">
@@ -47995,10 +47994,10 @@
       <c r="A109" s="51" t="s">
         <v>458</v>
       </c>
-      <c r="B109" s="59">
+      <c r="B109">
         <v>463267</v>
       </c>
-      <c r="C109" s="59">
+      <c r="C109">
         <v>455883</v>
       </c>
       <c r="D109" s="49">
@@ -48009,10 +48008,10 @@
       <c r="A110" s="51" t="s">
         <v>196</v>
       </c>
-      <c r="B110" s="59">
+      <c r="B110">
         <v>115443</v>
       </c>
-      <c r="C110" s="59">
+      <c r="C110">
         <v>113542</v>
       </c>
       <c r="D110" s="49">
@@ -48023,10 +48022,10 @@
       <c r="A111" s="51" t="s">
         <v>220</v>
       </c>
-      <c r="B111" s="59">
+      <c r="B111">
         <v>85226</v>
       </c>
-      <c r="C111" s="59">
+      <c r="C111">
         <v>83787</v>
       </c>
       <c r="D111" s="49">
@@ -48037,10 +48036,10 @@
       <c r="A112" s="51" t="s">
         <v>371</v>
       </c>
-      <c r="B112" s="59">
+      <c r="B112">
         <v>172414</v>
       </c>
-      <c r="C112" s="59">
+      <c r="C112">
         <v>169481</v>
       </c>
       <c r="D112" s="49">
@@ -48051,10 +48050,10 @@
       <c r="A113" s="51" t="s">
         <v>408</v>
       </c>
-      <c r="B113" s="59">
+      <c r="B113">
         <v>475980</v>
       </c>
-      <c r="C113" s="59">
+      <c r="C113">
         <v>467877</v>
       </c>
       <c r="D113" s="49">
@@ -48065,10 +48064,10 @@
       <c r="A114" s="51" t="s">
         <v>357</v>
       </c>
-      <c r="B114" s="59">
+      <c r="B114">
         <v>53241</v>
       </c>
-      <c r="C114" s="59">
+      <c r="C114">
         <v>52302</v>
       </c>
       <c r="D114" s="49">
@@ -48079,10 +48078,10 @@
       <c r="A115" s="51" t="s">
         <v>350</v>
       </c>
-      <c r="B115" s="59">
+      <c r="B115">
         <v>69858</v>
       </c>
-      <c r="C115" s="59">
+      <c r="C115">
         <v>68606</v>
       </c>
       <c r="D115" s="49">
@@ -48093,10 +48092,10 @@
       <c r="A116" s="51" t="s">
         <v>390</v>
       </c>
-      <c r="B116" s="59">
+      <c r="B116">
         <v>76625</v>
       </c>
-      <c r="C116" s="59">
+      <c r="C116">
         <v>75210</v>
       </c>
       <c r="D116" s="49">
@@ -48107,10 +48106,10 @@
       <c r="A117" s="51" t="s">
         <v>219</v>
       </c>
-      <c r="B117" s="59">
+      <c r="B117">
         <v>85362</v>
       </c>
-      <c r="C117" s="59">
+      <c r="C117">
         <v>83765</v>
       </c>
       <c r="D117" s="49">
@@ -48121,10 +48120,10 @@
       <c r="A118" s="51" t="s">
         <v>453</v>
       </c>
-      <c r="B118" s="59">
+      <c r="B118">
         <v>4389200</v>
       </c>
-      <c r="C118" s="59">
+      <c r="C118">
         <v>4306810</v>
       </c>
       <c r="D118" s="49">
@@ -48135,10 +48134,10 @@
       <c r="A119" s="51" t="s">
         <v>373</v>
       </c>
-      <c r="B119" s="59">
+      <c r="B119">
         <v>151306</v>
       </c>
-      <c r="C119" s="59">
+      <c r="C119">
         <v>148354</v>
       </c>
       <c r="D119" s="49">
@@ -48149,10 +48148,10 @@
       <c r="A120" s="51" t="s">
         <v>474</v>
       </c>
-      <c r="B120" s="59">
+      <c r="B120">
         <v>90350</v>
       </c>
-      <c r="C120" s="59">
+      <c r="C120">
         <v>88575</v>
       </c>
       <c r="D120" s="49">
@@ -48163,10 +48162,10 @@
       <c r="A121" s="51" t="s">
         <v>417</v>
       </c>
-      <c r="B121" s="59">
+      <c r="B121">
         <v>117408</v>
       </c>
-      <c r="C121" s="59">
+      <c r="C121">
         <v>115048</v>
       </c>
       <c r="D121" s="49">
@@ -48177,10 +48176,10 @@
       <c r="A122" s="51" t="s">
         <v>224</v>
       </c>
-      <c r="B122" s="59">
+      <c r="B122">
         <v>67135</v>
       </c>
-      <c r="C122" s="59">
+      <c r="C122">
         <v>65720</v>
       </c>
       <c r="D122" s="49">
@@ -48191,10 +48190,10 @@
       <c r="A123" s="51" t="s">
         <v>217</v>
       </c>
-      <c r="B123" s="59">
+      <c r="B123">
         <v>91583</v>
       </c>
-      <c r="C123" s="59">
+      <c r="C123">
         <v>89599</v>
       </c>
       <c r="D123" s="49">
@@ -48205,10 +48204,10 @@
       <c r="A124" s="51" t="s">
         <v>380</v>
       </c>
-      <c r="B124" s="59">
+      <c r="B124">
         <v>106232</v>
       </c>
-      <c r="C124" s="59">
+      <c r="C124">
         <v>103911</v>
       </c>
       <c r="D124" s="49">
@@ -48219,10 +48218,10 @@
       <c r="A125" s="51" t="s">
         <v>426</v>
       </c>
-      <c r="B125" s="59">
+      <c r="B125">
         <v>70064</v>
       </c>
-      <c r="C125" s="59">
+      <c r="C125">
         <v>68489</v>
       </c>
       <c r="D125" s="49">
@@ -48233,10 +48232,10 @@
       <c r="A126" s="51" t="s">
         <v>361</v>
       </c>
-      <c r="B126" s="59">
+      <c r="B126">
         <v>875199</v>
       </c>
-      <c r="C126" s="59">
+      <c r="C126">
         <v>855121</v>
       </c>
       <c r="D126" s="49">
@@ -48247,10 +48246,10 @@
       <c r="A127" s="51" t="s">
         <v>472</v>
       </c>
-      <c r="B127" s="59">
+      <c r="B127">
         <v>98642</v>
       </c>
-      <c r="C127" s="59">
+      <c r="C127">
         <v>96350</v>
       </c>
       <c r="D127" s="49">
@@ -48261,10 +48260,10 @@
       <c r="A128" s="51" t="s">
         <v>414</v>
       </c>
-      <c r="B128" s="59">
+      <c r="B128">
         <v>165122</v>
       </c>
-      <c r="C128" s="59">
+      <c r="C128">
         <v>161238</v>
       </c>
       <c r="D128" s="49">
@@ -48275,10 +48274,10 @@
       <c r="A129" s="51" t="s">
         <v>393</v>
       </c>
-      <c r="B129" s="59">
+      <c r="B129">
         <v>70403</v>
       </c>
-      <c r="C129" s="59">
+      <c r="C129">
         <v>68700</v>
       </c>
       <c r="D129" s="49">
@@ -48289,10 +48288,10 @@
       <c r="A130" s="51" t="s">
         <v>398</v>
       </c>
-      <c r="B130" s="59">
+      <c r="B130">
         <v>59514</v>
       </c>
-      <c r="C130" s="59">
+      <c r="C130">
         <v>58054</v>
       </c>
       <c r="D130" s="49">
@@ -48303,10 +48302,10 @@
       <c r="A131" s="51" t="s">
         <v>412</v>
       </c>
-      <c r="B131" s="59">
+      <c r="B131">
         <v>220544</v>
       </c>
-      <c r="C131" s="59">
+      <c r="C131">
         <v>214584</v>
       </c>
       <c r="D131" s="49">
@@ -48317,10 +48316,10 @@
       <c r="A132" s="51" t="s">
         <v>329</v>
       </c>
-      <c r="B132" s="59">
+      <c r="B132">
         <v>482194</v>
       </c>
-      <c r="C132" s="59">
+      <c r="C132">
         <v>468924</v>
       </c>
       <c r="D132" s="49">
@@ -48331,10 +48330,10 @@
       <c r="A133" s="51" t="s">
         <v>431</v>
       </c>
-      <c r="B133" s="59">
+      <c r="B133">
         <v>53933</v>
       </c>
-      <c r="C133" s="59">
+      <c r="C133">
         <v>52432</v>
       </c>
       <c r="D133" s="49">
@@ -48345,10 +48344,10 @@
       <c r="A134" s="51" t="s">
         <v>365</v>
       </c>
-      <c r="B134" s="59">
+      <c r="B134">
         <v>286070</v>
       </c>
-      <c r="C134" s="59">
+      <c r="C134">
         <v>278078</v>
       </c>
       <c r="D134" s="49">
@@ -48359,10 +48358,10 @@
       <c r="A135" s="51" t="s">
         <v>430</v>
       </c>
-      <c r="B135" s="59">
+      <c r="B135">
         <v>56837</v>
       </c>
-      <c r="C135" s="59">
+      <c r="C135">
         <v>55231</v>
       </c>
       <c r="D135" s="49">
@@ -48373,10 +48372,10 @@
       <c r="A136" s="51" t="s">
         <v>222</v>
       </c>
-      <c r="B136" s="59">
+      <c r="B136">
         <v>73491</v>
       </c>
-      <c r="C136" s="59">
+      <c r="C136">
         <v>71400</v>
       </c>
       <c r="D136" s="49">
@@ -48387,10 +48386,10 @@
       <c r="A137" s="51" t="s">
         <v>410</v>
       </c>
-      <c r="B137" s="59">
+      <c r="B137">
         <v>309689</v>
       </c>
-      <c r="C137" s="59">
+      <c r="C137">
         <v>300500</v>
       </c>
       <c r="D137" s="49">
@@ -48401,10 +48400,10 @@
       <c r="A138" s="51" t="s">
         <v>214</v>
       </c>
-      <c r="B138" s="59">
+      <c r="B138">
         <v>119578</v>
       </c>
-      <c r="C138" s="59">
+      <c r="C138">
         <v>116005</v>
       </c>
       <c r="D138" s="49">
@@ -48415,10 +48414,10 @@
       <c r="A139" s="51" t="s">
         <v>335</v>
       </c>
-      <c r="B139" s="59">
+      <c r="B139">
         <v>260956</v>
       </c>
-      <c r="C139" s="59">
+      <c r="C139">
         <v>252906</v>
       </c>
       <c r="D139" s="49">
@@ -48429,10 +48428,10 @@
       <c r="A140" s="51" t="s">
         <v>320</v>
       </c>
-      <c r="B140" s="59">
+      <c r="B140">
         <v>59990</v>
       </c>
-      <c r="C140" s="59">
+      <c r="C140">
         <v>58069</v>
       </c>
       <c r="D140" s="49">
@@ -48443,10 +48442,10 @@
       <c r="A141" s="51" t="s">
         <v>416</v>
       </c>
-      <c r="B141" s="59">
+      <c r="B141">
         <v>155406</v>
       </c>
-      <c r="C141" s="59">
+      <c r="C141">
         <v>150415</v>
       </c>
       <c r="D141" s="49">
@@ -48457,10 +48456,10 @@
       <c r="A142" s="51" t="s">
         <v>457</v>
       </c>
-      <c r="B142" s="59">
+      <c r="B142">
         <v>489465</v>
       </c>
-      <c r="C142" s="59">
+      <c r="C142">
         <v>473517</v>
       </c>
       <c r="D142" s="49">
@@ -48471,10 +48470,10 @@
       <c r="A143" s="51" t="s">
         <v>209</v>
       </c>
-      <c r="B143" s="59">
+      <c r="B143">
         <v>154861</v>
       </c>
-      <c r="C143" s="59">
+      <c r="C143">
         <v>149723</v>
       </c>
       <c r="D143" s="49">
@@ -48485,10 +48484,10 @@
       <c r="A144" s="51" t="s">
         <v>199</v>
       </c>
-      <c r="B144" s="59">
+      <c r="B144">
         <v>74824</v>
       </c>
-      <c r="C144" s="59">
+      <c r="C144">
         <v>72313</v>
       </c>
       <c r="D144" s="49">
@@ -48499,10 +48498,10 @@
       <c r="A145" s="51" t="s">
         <v>375</v>
       </c>
-      <c r="B145" s="59">
+      <c r="B145">
         <v>128347</v>
       </c>
-      <c r="C145" s="59">
+      <c r="C145">
         <v>123914</v>
       </c>
       <c r="D145" s="49">
@@ -48513,10 +48512,10 @@
       <c r="A146" s="51" t="s">
         <v>348</v>
       </c>
-      <c r="B146" s="59">
+      <c r="B146">
         <v>75960</v>
       </c>
-      <c r="C146" s="59">
+      <c r="C146">
         <v>73210</v>
       </c>
       <c r="D146" s="49">
@@ -48527,10 +48526,10 @@
       <c r="A147" s="51" t="s">
         <v>310</v>
       </c>
-      <c r="B147" s="59">
+      <c r="B147">
         <v>94208</v>
       </c>
-      <c r="C147" s="59">
+      <c r="C147">
         <v>90647</v>
       </c>
       <c r="D147" s="49">
@@ -48541,10 +48540,10 @@
       <c r="A148" s="51" t="s">
         <v>226</v>
       </c>
-      <c r="B148" s="59">
+      <c r="B148">
         <v>64898</v>
       </c>
-      <c r="C148" s="59">
+      <c r="C148">
         <v>62444</v>
       </c>
       <c r="D148" s="49">
@@ -48555,10 +48554,10 @@
       <c r="A149" s="51" t="s">
         <v>395</v>
       </c>
-      <c r="B149" s="59">
+      <c r="B149">
         <v>62186</v>
       </c>
-      <c r="C149" s="59">
+      <c r="C149">
         <v>59806</v>
       </c>
       <c r="D149" s="49">
@@ -48569,10 +48568,10 @@
       <c r="A150" s="51" t="s">
         <v>229</v>
       </c>
-      <c r="B150" s="59">
+      <c r="B150">
         <v>56416</v>
       </c>
-      <c r="C150" s="59">
+      <c r="C150">
         <v>54252</v>
       </c>
       <c r="D150" s="49">
@@ -48583,10 +48582,10 @@
       <c r="A151" s="51" t="s">
         <v>257</v>
       </c>
-      <c r="B151" s="59">
+      <c r="B151">
         <v>63910</v>
       </c>
-      <c r="C151" s="59">
+      <c r="C151">
         <v>61435</v>
       </c>
       <c r="D151" s="49">
@@ -48597,10 +48596,10 @@
       <c r="A152" s="51" t="s">
         <v>332</v>
       </c>
-      <c r="B152" s="59">
+      <c r="B152">
         <v>293976</v>
       </c>
-      <c r="C152" s="59">
+      <c r="C152">
         <v>282449</v>
       </c>
       <c r="D152" s="49">
@@ -48611,10 +48610,10 @@
       <c r="A153" s="51" t="s">
         <v>318</v>
       </c>
-      <c r="B153" s="59">
+      <c r="B153">
         <v>66443</v>
       </c>
-      <c r="C153" s="59">
+      <c r="C153">
         <v>63812</v>
       </c>
       <c r="D153" s="49">
@@ -48625,10 +48624,10 @@
       <c r="A154" s="51" t="s">
         <v>211</v>
       </c>
-      <c r="B154" s="59">
+      <c r="B154">
         <v>147299</v>
       </c>
-      <c r="C154" s="59">
+      <c r="C154">
         <v>141419</v>
       </c>
       <c r="D154" s="49">
@@ -48639,10 +48638,10 @@
       <c r="A155" s="51" t="s">
         <v>206</v>
       </c>
-      <c r="B155" s="59">
+      <c r="B155">
         <v>177055</v>
       </c>
-      <c r="C155" s="59">
+      <c r="C155">
         <v>169961</v>
       </c>
       <c r="D155" s="49">
@@ -48653,10 +48652,10 @@
       <c r="A156" s="51" t="s">
         <v>268</v>
       </c>
-      <c r="B156" s="59">
+      <c r="B156">
         <v>139766</v>
       </c>
-      <c r="C156" s="59">
+      <c r="C156">
         <v>134126</v>
       </c>
       <c r="D156" s="49">
@@ -48667,10 +48666,10 @@
       <c r="A157" s="51" t="s">
         <v>311</v>
       </c>
-      <c r="B157" s="59">
+      <c r="B157">
         <v>86882</v>
       </c>
-      <c r="C157" s="59">
+      <c r="C157">
         <v>83353</v>
       </c>
       <c r="D157" s="49">
@@ -48681,10 +48680,10 @@
       <c r="A158" s="51" t="s">
         <v>228</v>
       </c>
-      <c r="B158" s="59">
+      <c r="B158">
         <v>62734</v>
       </c>
-      <c r="C158" s="59">
+      <c r="C158">
         <v>60141</v>
       </c>
       <c r="D158" s="49">
@@ -48695,10 +48694,10 @@
       <c r="A159" s="51" t="s">
         <v>276</v>
       </c>
-      <c r="B159" s="59">
+      <c r="B159">
         <v>97040</v>
       </c>
-      <c r="C159" s="59">
+      <c r="C159">
         <v>92968</v>
       </c>
       <c r="D159" s="49">
@@ -48709,10 +48708,10 @@
       <c r="A160" s="51" t="s">
         <v>157</v>
       </c>
-      <c r="B160" s="59">
+      <c r="B160">
         <v>55946</v>
       </c>
-      <c r="C160" s="59">
+      <c r="C160">
         <v>53593</v>
       </c>
       <c r="D160" s="49">
@@ -48723,10 +48722,10 @@
       <c r="A161" s="51" t="s">
         <v>325</v>
       </c>
-      <c r="B161" s="59">
+      <c r="B161">
         <v>1275750</v>
       </c>
-      <c r="C161" s="59">
+      <c r="C161">
         <v>1222027</v>
       </c>
       <c r="D161" s="49">
@@ -48737,10 +48736,10 @@
       <c r="A162" s="51" t="s">
         <v>337</v>
       </c>
-      <c r="B162" s="59">
+      <c r="B162">
         <v>218184</v>
       </c>
-      <c r="C162" s="59">
+      <c r="C162">
         <v>208962</v>
       </c>
       <c r="D162" s="49">
@@ -48751,10 +48750,10 @@
       <c r="A163" s="51" t="s">
         <v>331</v>
       </c>
-      <c r="B163" s="59">
+      <c r="B163">
         <v>330544</v>
       </c>
-      <c r="C163" s="59">
+      <c r="C163">
         <v>316257</v>
       </c>
       <c r="D163" s="49">
@@ -48765,10 +48764,10 @@
       <c r="A164" s="51" t="s">
         <v>248</v>
       </c>
-      <c r="B164" s="59">
+      <c r="B164">
         <v>90750</v>
       </c>
-      <c r="C164" s="59">
+      <c r="C164">
         <v>86807</v>
       </c>
       <c r="D164" s="49">
@@ -48779,10 +48778,10 @@
       <c r="A165" s="51" t="s">
         <v>290</v>
       </c>
-      <c r="B165" s="59">
+      <c r="B165">
         <v>52354</v>
       </c>
-      <c r="C165" s="59">
+      <c r="C165">
         <v>50023</v>
       </c>
       <c r="D165" s="49">
@@ -48793,10 +48792,10 @@
       <c r="A166" s="51" t="s">
         <v>333</v>
       </c>
-      <c r="B166" s="59">
+      <c r="B166">
         <v>287376</v>
       </c>
-      <c r="C166" s="59">
+      <c r="C166">
         <v>274465</v>
       </c>
       <c r="D166" s="49">
@@ -48807,10 +48806,10 @@
       <c r="A167" s="51" t="s">
         <v>282</v>
       </c>
-      <c r="B167" s="59">
+      <c r="B167">
         <v>72370</v>
       </c>
-      <c r="C167" s="59">
+      <c r="C167">
         <v>69098</v>
       </c>
       <c r="D167" s="49">
@@ -48821,10 +48820,10 @@
       <c r="A168" s="51" t="s">
         <v>289</v>
       </c>
-      <c r="B168" s="59">
+      <c r="B168">
         <v>52902</v>
       </c>
-      <c r="C168" s="59">
+      <c r="C168">
         <v>50439</v>
       </c>
       <c r="D168" s="49">
@@ -48835,10 +48834,10 @@
       <c r="A169" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="B169" s="59">
+      <c r="B169">
         <v>156489</v>
       </c>
-      <c r="C169" s="59">
+      <c r="C169">
         <v>149120</v>
       </c>
       <c r="D169" s="49">
@@ -48849,10 +48848,10 @@
       <c r="A170" s="51" t="s">
         <v>411</v>
       </c>
-      <c r="B170" s="59">
+      <c r="B170">
         <v>277357</v>
       </c>
-      <c r="C170" s="59">
+      <c r="C170">
         <v>264260</v>
       </c>
       <c r="D170" s="49">
@@ -48863,10 +48862,10 @@
       <c r="A171" s="51" t="s">
         <v>387</v>
       </c>
-      <c r="B171" s="59">
+      <c r="B171">
         <v>83961</v>
       </c>
-      <c r="C171" s="59">
+      <c r="C171">
         <v>79914</v>
       </c>
       <c r="D171" s="49">
@@ -48877,10 +48876,10 @@
       <c r="A172" s="51" t="s">
         <v>210</v>
       </c>
-      <c r="B172" s="59">
+      <c r="B172">
         <v>150487</v>
       </c>
-      <c r="C172" s="59">
+      <c r="C172">
         <v>143232</v>
       </c>
       <c r="D172" s="49">
@@ -48891,10 +48890,10 @@
       <c r="A173" s="51" t="s">
         <v>299</v>
       </c>
-      <c r="B173" s="59">
+      <c r="B173">
         <v>164091</v>
       </c>
-      <c r="C173" s="59">
+      <c r="C173">
         <v>156159</v>
       </c>
       <c r="D173" s="49">
@@ -48905,10 +48904,10 @@
       <c r="A174" s="51" t="s">
         <v>223</v>
       </c>
-      <c r="B174" s="59">
+      <c r="B174">
         <v>70734</v>
       </c>
-      <c r="C174" s="59">
+      <c r="C174">
         <v>67302</v>
       </c>
       <c r="D174" s="49">
@@ -48919,10 +48918,10 @@
       <c r="A175" s="51" t="s">
         <v>273</v>
       </c>
-      <c r="B175" s="59">
+      <c r="B175">
         <v>102873</v>
       </c>
-      <c r="C175" s="59">
+      <c r="C175">
         <v>97808</v>
       </c>
       <c r="D175" s="49">
@@ -48933,10 +48932,10 @@
       <c r="A176" s="51" t="s">
         <v>256</v>
       </c>
-      <c r="B176" s="59">
+      <c r="B176">
         <v>76898</v>
       </c>
-      <c r="C176" s="59">
+      <c r="C176">
         <v>73093</v>
       </c>
       <c r="D176" s="49">
@@ -48947,10 +48946,10 @@
       <c r="A177" s="51" t="s">
         <v>252</v>
       </c>
-      <c r="B177" s="59">
+      <c r="B177">
         <v>545683</v>
       </c>
-      <c r="C177" s="59">
+      <c r="C177">
         <v>518394</v>
       </c>
       <c r="D177" s="49">
@@ -48961,10 +48960,10 @@
       <c r="A178" s="51" t="s">
         <v>204</v>
       </c>
-      <c r="B178" s="59">
+      <c r="B178">
         <v>359750</v>
       </c>
-      <c r="C178" s="59">
+      <c r="C178">
         <v>341739</v>
       </c>
       <c r="D178" s="49">
@@ -48975,10 +48974,10 @@
       <c r="A179" s="51" t="s">
         <v>212</v>
       </c>
-      <c r="B179" s="59">
+      <c r="B179">
         <v>128139</v>
       </c>
-      <c r="C179" s="59">
+      <c r="C179">
         <v>121701</v>
       </c>
       <c r="D179" s="49">
@@ -48989,10 +48988,10 @@
       <c r="A180" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="B180" s="59">
+      <c r="B180">
         <v>52078</v>
       </c>
-      <c r="C180" s="59">
+      <c r="C180">
         <v>49450</v>
       </c>
       <c r="D180" s="49">
@@ -49003,10 +49002,10 @@
       <c r="A181" s="51" t="s">
         <v>343</v>
       </c>
-      <c r="B181" s="59">
+      <c r="B181">
         <v>157628</v>
       </c>
-      <c r="C181" s="59">
+      <c r="C181">
         <v>149563</v>
       </c>
       <c r="D181" s="49">
@@ -49017,10 +49016,10 @@
       <c r="A182" s="51" t="s">
         <v>272</v>
       </c>
-      <c r="B182" s="59">
+      <c r="B182">
         <v>108234</v>
       </c>
-      <c r="C182" s="59">
+      <c r="C182">
         <v>102657</v>
       </c>
       <c r="D182" s="49">
@@ -49031,10 +49030,10 @@
       <c r="A183" s="51" t="s">
         <v>353</v>
       </c>
-      <c r="B183" s="59">
+      <c r="B183">
         <v>60857</v>
       </c>
-      <c r="C183" s="59">
+      <c r="C183">
         <v>57716</v>
       </c>
       <c r="D183" s="49">
@@ -49045,10 +49044,10 @@
       <c r="A184" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="B184" s="59">
+      <c r="B184">
         <v>51941</v>
       </c>
-      <c r="C184" s="59">
+      <c r="C184">
         <v>49236</v>
       </c>
       <c r="D184" s="49">
@@ -49059,10 +49058,10 @@
       <c r="A185" s="51" t="s">
         <v>119</v>
       </c>
-      <c r="B185" s="59">
+      <c r="B185">
         <v>143273</v>
       </c>
-      <c r="C185" s="59">
+      <c r="C185">
         <v>135787</v>
       </c>
       <c r="D185" s="49">
@@ -49073,10 +49072,10 @@
       <c r="A186" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="B186" s="59">
+      <c r="B186">
         <v>84927</v>
       </c>
-      <c r="C186" s="59">
+      <c r="C186">
         <v>80436</v>
       </c>
       <c r="D186" s="49">
@@ -49087,10 +49086,10 @@
       <c r="A187" s="51" t="s">
         <v>433</v>
       </c>
-      <c r="B187" s="59">
+      <c r="B187">
         <v>54720</v>
       </c>
-      <c r="C187" s="59">
+      <c r="C187">
         <v>51808</v>
       </c>
       <c r="D187" s="49">
@@ -49101,10 +49100,10 @@
       <c r="A188" s="51" t="s">
         <v>249</v>
       </c>
-      <c r="B188" s="59">
+      <c r="B188">
         <v>66368</v>
       </c>
-      <c r="C188" s="59">
+      <c r="C188">
         <v>62784</v>
       </c>
       <c r="D188" s="49">
@@ -49115,10 +49114,10 @@
       <c r="A189" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="B189" s="59">
+      <c r="B189">
         <v>283340</v>
       </c>
-      <c r="C189" s="59">
+      <c r="C189">
         <v>268020</v>
       </c>
       <c r="D189" s="49">
@@ -49129,10 +49128,10 @@
       <c r="A190" s="51" t="s">
         <v>292</v>
       </c>
-      <c r="B190" s="59">
+      <c r="B190">
         <v>51410</v>
       </c>
-      <c r="C190" s="59">
+      <c r="C190">
         <v>48626</v>
       </c>
       <c r="D190" s="49">
@@ -49143,10 +49142,10 @@
       <c r="A191" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="B191" s="59">
+      <c r="B191">
         <v>77882</v>
       </c>
-      <c r="C191" s="59">
+      <c r="C191">
         <v>73590</v>
       </c>
       <c r="D191" s="49">
@@ -49157,10 +49156,10 @@
       <c r="A192" s="51" t="s">
         <v>360</v>
       </c>
-      <c r="B192" s="59">
+      <c r="B192">
         <v>3985240</v>
       </c>
-      <c r="C192" s="59">
+      <c r="C192">
         <v>3764094</v>
       </c>
       <c r="D192" s="49">
@@ -49171,10 +49170,10 @@
       <c r="A193" s="51" t="s">
         <v>342</v>
       </c>
-      <c r="B193" s="59">
+      <c r="B193">
         <v>165125</v>
       </c>
-      <c r="C193" s="59">
+      <c r="C193">
         <v>155911</v>
       </c>
       <c r="D193" s="49">
@@ -49185,10 +49184,10 @@
       <c r="A194" s="51" t="s">
         <v>144</v>
       </c>
-      <c r="B194" s="59">
+      <c r="B194">
         <v>71475</v>
       </c>
-      <c r="C194" s="59">
+      <c r="C194">
         <v>67454</v>
       </c>
       <c r="D194" s="49">
@@ -49199,10 +49198,10 @@
       <c r="A195" s="51" t="s">
         <v>253</v>
       </c>
-      <c r="B195" s="59">
+      <c r="B195">
         <v>232995</v>
       </c>
-      <c r="C195" s="59">
+      <c r="C195">
         <v>219856</v>
       </c>
       <c r="D195" s="49">
@@ -49213,10 +49212,10 @@
       <c r="A196" s="51" t="s">
         <v>469</v>
       </c>
-      <c r="B196" s="59">
+      <c r="B196">
         <v>118133</v>
       </c>
-      <c r="C196" s="59">
+      <c r="C196">
         <v>111374</v>
       </c>
       <c r="D196" s="49">
@@ -49227,10 +49226,10 @@
       <c r="A197" s="51" t="s">
         <v>227</v>
       </c>
-      <c r="B197" s="59">
+      <c r="B197">
         <v>65334</v>
       </c>
-      <c r="C197" s="59">
+      <c r="C197">
         <v>61560</v>
       </c>
       <c r="D197" s="49">
@@ -49241,10 +49240,10 @@
       <c r="A198" s="51" t="s">
         <v>264</v>
       </c>
-      <c r="B198" s="59">
+      <c r="B198">
         <v>265291</v>
       </c>
-      <c r="C198" s="59">
+      <c r="C198">
         <v>249924</v>
       </c>
       <c r="D198" s="49">
@@ -49255,10 +49254,10 @@
       <c r="A199" s="51" t="s">
         <v>283</v>
       </c>
-      <c r="B199" s="59">
+      <c r="B199">
         <v>68672</v>
       </c>
-      <c r="C199" s="59">
+      <c r="C199">
         <v>64689</v>
       </c>
       <c r="D199" s="49">
@@ -49269,10 +49268,10 @@
       <c r="A200" s="51" t="s">
         <v>246</v>
       </c>
-      <c r="B200" s="59">
+      <c r="B200">
         <v>138826</v>
       </c>
-      <c r="C200" s="59">
+      <c r="C200">
         <v>130749</v>
       </c>
       <c r="D200" s="49">
@@ -49283,10 +49282,10 @@
       <c r="A201" s="51" t="s">
         <v>305</v>
       </c>
-      <c r="B201" s="59">
+      <c r="B201">
         <v>115971</v>
       </c>
-      <c r="C201" s="59">
+      <c r="C201">
         <v>109161</v>
       </c>
       <c r="D201" s="49">
@@ -49297,10 +49296,10 @@
       <c r="A202" s="51" t="s">
         <v>251</v>
       </c>
-      <c r="B202" s="59">
+      <c r="B202">
         <v>578339</v>
       </c>
-      <c r="C202" s="59">
+      <c r="C202">
         <v>544216</v>
       </c>
       <c r="D202" s="49">
@@ -49311,10 +49310,10 @@
       <c r="A203" s="51" t="s">
         <v>306</v>
       </c>
-      <c r="B203" s="59">
+      <c r="B203">
         <v>115545</v>
       </c>
-      <c r="C203" s="59">
+      <c r="C203">
         <v>108665</v>
       </c>
       <c r="D203" s="49">
@@ -49325,10 +49324,10 @@
       <c r="A204" s="51" t="s">
         <v>340</v>
       </c>
-      <c r="B204" s="59">
+      <c r="B204">
         <v>193854</v>
       </c>
-      <c r="C204" s="59">
+      <c r="C204">
         <v>182239</v>
       </c>
       <c r="D204" s="49">
@@ -49339,10 +49338,10 @@
       <c r="A205" s="51" t="s">
         <v>345</v>
       </c>
-      <c r="B205" s="59">
+      <c r="B205">
         <v>105164</v>
       </c>
-      <c r="C205" s="59">
+      <c r="C205">
         <v>98852</v>
       </c>
       <c r="D205" s="49">
@@ -49353,10 +49352,10 @@
       <c r="A206" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="B206" s="59">
+      <c r="B206">
         <v>61936</v>
       </c>
-      <c r="C206" s="59">
+      <c r="C206">
         <v>58211</v>
       </c>
       <c r="D206" s="49">
@@ -49367,10 +49366,10 @@
       <c r="A207" s="51" t="s">
         <v>155</v>
       </c>
-      <c r="B207" s="59">
+      <c r="B207">
         <v>57560</v>
       </c>
-      <c r="C207" s="59">
+      <c r="C207">
         <v>54034</v>
       </c>
       <c r="D207" s="49">
@@ -49381,10 +49380,10 @@
       <c r="A208" s="51" t="s">
         <v>347</v>
       </c>
-      <c r="B208" s="59">
+      <c r="B208">
         <v>93135</v>
       </c>
-      <c r="C208" s="59">
+      <c r="C208">
         <v>87329</v>
       </c>
       <c r="D208" s="49">
@@ -49395,10 +49394,10 @@
       <c r="A209" s="51" t="s">
         <v>313</v>
       </c>
-      <c r="B209" s="59">
+      <c r="B209">
         <v>83568</v>
       </c>
-      <c r="C209" s="59">
+      <c r="C209">
         <v>78357</v>
       </c>
       <c r="D209" s="49">
@@ -49409,10 +49408,10 @@
       <c r="A210" s="51" t="s">
         <v>418</v>
       </c>
-      <c r="B210" s="59">
+      <c r="B210">
         <v>110279</v>
       </c>
-      <c r="C210" s="59">
+      <c r="C210">
         <v>103314</v>
       </c>
       <c r="D210" s="49">
@@ -49423,10 +49422,10 @@
       <c r="A211" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="B211" s="59">
+      <c r="B211">
         <v>82023</v>
       </c>
-      <c r="C211" s="59">
+      <c r="C211">
         <v>76762</v>
       </c>
       <c r="D211" s="49">
@@ -49437,10 +49436,10 @@
       <c r="A212" s="51" t="s">
         <v>359</v>
       </c>
-      <c r="B212" s="59">
+      <c r="B212">
         <v>51881</v>
       </c>
-      <c r="C212" s="59">
+      <c r="C212">
         <v>48535</v>
       </c>
       <c r="D212" s="49">
@@ -49451,10 +49450,10 @@
       <c r="A213" s="51" t="s">
         <v>307</v>
       </c>
-      <c r="B213" s="59">
+      <c r="B213">
         <v>112280</v>
       </c>
-      <c r="C213" s="59">
+      <c r="C213">
         <v>105027</v>
       </c>
       <c r="D213" s="49">
@@ -49465,10 +49464,10 @@
       <c r="A214" s="51" t="s">
         <v>91</v>
       </c>
-      <c r="B214" s="59">
+      <c r="B214">
         <v>60080</v>
       </c>
-      <c r="C214" s="59">
+      <c r="C214">
         <v>56165</v>
       </c>
       <c r="D214" s="49">
@@ -49479,10 +49478,10 @@
       <c r="A215" s="51" t="s">
         <v>339</v>
       </c>
-      <c r="B215" s="59">
+      <c r="B215">
         <v>196344</v>
       </c>
-      <c r="C215" s="59">
+      <c r="C215">
         <v>183523</v>
       </c>
       <c r="D215" s="49">
@@ -49493,10 +49492,10 @@
       <c r="A216" s="51" t="s">
         <v>351</v>
       </c>
-      <c r="B216" s="59">
+      <c r="B216">
         <v>70375</v>
       </c>
-      <c r="C216" s="59">
+      <c r="C216">
         <v>65749</v>
       </c>
       <c r="D216" s="49">
@@ -49507,10 +49506,10 @@
       <c r="A217" s="51" t="s">
         <v>288</v>
       </c>
-      <c r="B217" s="59">
+      <c r="B217">
         <v>56397</v>
       </c>
-      <c r="C217" s="59">
+      <c r="C217">
         <v>52628</v>
       </c>
       <c r="D217" s="49">
@@ -49521,10 +49520,10 @@
       <c r="A218" s="51" t="s">
         <v>349</v>
       </c>
-      <c r="B218" s="59">
+      <c r="B218">
         <v>75655</v>
       </c>
-      <c r="C218" s="59">
+      <c r="C218">
         <v>70582</v>
       </c>
       <c r="D218" s="49">
@@ -49535,10 +49534,10 @@
       <c r="A219" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="B219" s="59">
+      <c r="B219">
         <v>60229</v>
       </c>
-      <c r="C219" s="59">
+      <c r="C219">
         <v>56180</v>
       </c>
       <c r="D219" s="49">
@@ -49549,10 +49548,10 @@
       <c r="A220" s="51" t="s">
         <v>218</v>
       </c>
-      <c r="B220" s="59">
+      <c r="B220">
         <v>90810</v>
       </c>
-      <c r="C220" s="59">
+      <c r="C220">
         <v>84664</v>
       </c>
       <c r="D220" s="49">
@@ -49563,10 +49562,10 @@
       <c r="A221" s="51" t="s">
         <v>344</v>
       </c>
-      <c r="B221" s="59">
+      <c r="B221">
         <v>147714</v>
       </c>
-      <c r="C221" s="59">
+      <c r="C221">
         <v>137635</v>
       </c>
       <c r="D221" s="49">
@@ -49577,10 +49576,10 @@
       <c r="A222" s="51" t="s">
         <v>338</v>
       </c>
-      <c r="B222" s="59">
+      <c r="B222">
         <v>198151</v>
       </c>
-      <c r="C222" s="59">
+      <c r="C222">
         <v>184603</v>
       </c>
       <c r="D222" s="49">
@@ -49591,10 +49590,10 @@
       <c r="A223" s="51" t="s">
         <v>197</v>
       </c>
-      <c r="B223" s="59">
+      <c r="B223">
         <v>79743</v>
       </c>
-      <c r="C223" s="59">
+      <c r="C223">
         <v>74276</v>
       </c>
       <c r="D223" s="49">
@@ -49605,10 +49604,10 @@
       <c r="A224" s="51" t="s">
         <v>198</v>
       </c>
-      <c r="B224" s="59">
+      <c r="B224">
         <v>79348</v>
       </c>
-      <c r="C224" s="59">
+      <c r="C224">
         <v>73901</v>
       </c>
       <c r="D224" s="49">
@@ -49619,10 +49618,10 @@
       <c r="A225" s="51" t="s">
         <v>250</v>
       </c>
-      <c r="B225" s="59">
+      <c r="B225">
         <v>60535</v>
       </c>
-      <c r="C225" s="59">
+      <c r="C225">
         <v>56339</v>
       </c>
       <c r="D225" s="49">
@@ -49633,10 +49632,10 @@
       <c r="A226" s="51" t="s">
         <v>356</v>
       </c>
-      <c r="B226" s="59">
+      <c r="B226">
         <v>57543</v>
       </c>
-      <c r="C226" s="59">
+      <c r="C226">
         <v>53524</v>
       </c>
       <c r="D226" s="49">
@@ -49647,10 +49646,10 @@
       <c r="A227" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="B227" s="59">
+      <c r="B227">
         <v>80343</v>
       </c>
-      <c r="C227" s="59">
+      <c r="C227">
         <v>74676</v>
       </c>
       <c r="D227" s="49">
@@ -49661,10 +49660,10 @@
       <c r="A228" s="51" t="s">
         <v>355</v>
       </c>
-      <c r="B228" s="59">
+      <c r="B228">
         <v>58098</v>
       </c>
-      <c r="C228" s="59">
+      <c r="C228">
         <v>53987</v>
       </c>
       <c r="D228" s="49">
@@ -49675,10 +49674,10 @@
       <c r="A229" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="B229" s="59">
+      <c r="B229">
         <v>54155</v>
       </c>
-      <c r="C229" s="59">
+      <c r="C229">
         <v>50302</v>
       </c>
       <c r="D229" s="49">
@@ -49689,10 +49688,10 @@
       <c r="A230" s="51" t="s">
         <v>300</v>
       </c>
-      <c r="B230" s="59">
+      <c r="B230">
         <v>148801</v>
       </c>
-      <c r="C230" s="59">
+      <c r="C230">
         <v>138120</v>
       </c>
       <c r="D230" s="49">
@@ -49703,10 +49702,10 @@
       <c r="A231" s="51" t="s">
         <v>202</v>
       </c>
-      <c r="B231" s="59">
+      <c r="B231">
         <v>7319682</v>
       </c>
-      <c r="C231" s="59">
+      <c r="C231">
         <v>6792854</v>
       </c>
       <c r="D231" s="49">
@@ -49717,10 +49716,10 @@
       <c r="A232" s="51" t="s">
         <v>247</v>
       </c>
-      <c r="B232" s="59">
+      <c r="B232">
         <v>104267</v>
       </c>
-      <c r="C232" s="59">
+      <c r="C232">
         <v>96759</v>
       </c>
       <c r="D232" s="49">
@@ -49731,10 +49730,10 @@
       <c r="A233" s="51" t="s">
         <v>354</v>
       </c>
-      <c r="B233" s="59">
+      <c r="B233">
         <v>58256</v>
       </c>
-      <c r="C233" s="59">
+      <c r="C233">
         <v>54037</v>
       </c>
       <c r="D233" s="49">
@@ -49745,10 +49744,10 @@
       <c r="A234" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="B234" s="59">
+      <c r="B234">
         <v>56310</v>
       </c>
-      <c r="C234" s="59">
+      <c r="C234">
         <v>52230</v>
       </c>
       <c r="D234" s="49">
@@ -49759,10 +49758,10 @@
       <c r="A235" s="51" t="s">
         <v>205</v>
       </c>
-      <c r="B235" s="59">
+      <c r="B235">
         <v>301700</v>
       </c>
-      <c r="C235" s="59">
+      <c r="C235">
         <v>279709</v>
       </c>
       <c r="D235" s="49">
@@ -49773,10 +49772,10 @@
       <c r="A236" s="51" t="s">
         <v>266</v>
       </c>
-      <c r="B236" s="59">
+      <c r="B236">
         <v>150193</v>
       </c>
-      <c r="C236" s="59">
+      <c r="C236">
         <v>139245</v>
       </c>
       <c r="D236" s="49">
@@ -49787,10 +49786,10 @@
       <c r="A237" s="51" t="s">
         <v>287</v>
       </c>
-      <c r="B237" s="59">
+      <c r="B237">
         <v>59382</v>
       </c>
-      <c r="C237" s="59">
+      <c r="C237">
         <v>55048</v>
       </c>
       <c r="D237" s="49">
@@ -49801,10 +49800,10 @@
       <c r="A238" s="51" t="s">
         <v>254</v>
       </c>
-      <c r="B238" s="59">
+      <c r="B238">
         <v>189466</v>
       </c>
-      <c r="C238" s="59">
+      <c r="C238">
         <v>175607</v>
       </c>
       <c r="D238" s="49">
@@ -49815,10 +49814,10 @@
       <c r="A239" s="51" t="s">
         <v>432</v>
       </c>
-      <c r="B239" s="59">
+      <c r="B239">
         <v>59379</v>
       </c>
-      <c r="C239" s="59">
+      <c r="C239">
         <v>55026</v>
       </c>
       <c r="D239" s="49">
@@ -49829,10 +49828,10 @@
       <c r="A240" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="B240" s="59">
+      <c r="B240">
         <v>126964</v>
       </c>
-      <c r="C240" s="59">
+      <c r="C240">
         <v>117599</v>
       </c>
       <c r="D240" s="49">
@@ -49843,10 +49842,10 @@
       <c r="A241" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="B241" s="59">
+      <c r="B241">
         <v>61360</v>
       </c>
-      <c r="C241" s="59">
+      <c r="C241">
         <v>56797</v>
       </c>
       <c r="D241" s="49">
@@ -49857,10 +49856,10 @@
       <c r="A242" s="51" t="s">
         <v>73</v>
       </c>
-      <c r="B242" s="59">
+      <c r="B242">
         <v>246856</v>
       </c>
-      <c r="C242" s="59">
+      <c r="C242">
         <v>228294</v>
       </c>
       <c r="D242" s="49">
@@ -49871,10 +49870,10 @@
       <c r="A243" s="51" t="s">
         <v>334</v>
       </c>
-      <c r="B243" s="59">
+      <c r="B243">
         <v>286152</v>
       </c>
-      <c r="C243" s="59">
+      <c r="C243">
         <v>264412</v>
       </c>
       <c r="D243" s="49">
@@ -49885,10 +49884,10 @@
       <c r="A244" s="51" t="s">
         <v>185</v>
       </c>
-      <c r="B244" s="59">
+      <c r="B244">
         <v>55688</v>
       </c>
-      <c r="C244" s="59">
+      <c r="C244">
         <v>51388</v>
       </c>
       <c r="D244" s="49">
@@ -49899,10 +49898,10 @@
       <c r="A245" s="51" t="s">
         <v>317</v>
       </c>
-      <c r="B245" s="59">
+      <c r="B245">
         <v>67778</v>
       </c>
-      <c r="C245" s="59">
+      <c r="C245">
         <v>62524</v>
       </c>
       <c r="D245" s="49">
@@ -49913,10 +49912,10 @@
       <c r="A246" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="B246" s="59">
+      <c r="B246">
         <v>61906</v>
       </c>
-      <c r="C246" s="59">
+      <c r="C246">
         <v>57060</v>
       </c>
       <c r="D246" s="49">
@@ -49927,10 +49926,10 @@
       <c r="A247" s="51" t="s">
         <v>270</v>
       </c>
-      <c r="B247" s="59">
+      <c r="B247">
         <v>115463</v>
       </c>
-      <c r="C247" s="59">
+      <c r="C247">
         <v>106412</v>
       </c>
       <c r="D247" s="49">
@@ -49941,10 +49940,10 @@
       <c r="A248" s="51" t="s">
         <v>233</v>
       </c>
-      <c r="B248" s="59">
+      <c r="B248">
         <v>586634</v>
       </c>
-      <c r="C248" s="59">
+      <c r="C248">
         <v>540107</v>
       </c>
       <c r="D248" s="49">
@@ -49955,10 +49954,10 @@
       <c r="A249" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="B249" s="59">
+      <c r="B249">
         <v>64130</v>
       </c>
-      <c r="C249" s="59">
+      <c r="C249">
         <v>59043</v>
       </c>
       <c r="D249" s="49">
@@ -49969,10 +49968,10 @@
       <c r="A250" s="51" t="s">
         <v>295</v>
       </c>
-      <c r="B250" s="59">
+      <c r="B250">
         <v>946280</v>
       </c>
-      <c r="C250" s="59">
+      <c r="C250">
         <v>870911</v>
       </c>
       <c r="D250" s="49">
@@ -49983,10 +49982,10 @@
       <c r="A251" s="51" t="s">
         <v>260</v>
       </c>
-      <c r="B251" s="59">
+      <c r="B251">
         <v>1129348</v>
       </c>
-      <c r="C251" s="59">
+      <c r="C251">
         <v>1038099</v>
       </c>
       <c r="D251" s="49">
@@ -49997,10 +49996,10 @@
       <c r="A252" s="51" t="s">
         <v>231</v>
       </c>
-      <c r="B252" s="59">
+      <c r="B252">
         <v>696858</v>
       </c>
-      <c r="C252" s="59">
+      <c r="C252">
         <v>640273</v>
       </c>
       <c r="D252" s="49">
@@ -50011,10 +50010,10 @@
       <c r="A253" s="51" t="s">
         <v>297</v>
       </c>
-      <c r="B253" s="59">
+      <c r="B253">
         <v>315978</v>
       </c>
-      <c r="C253" s="59">
+      <c r="C253">
         <v>290304</v>
       </c>
       <c r="D253" s="49">
@@ -50025,10 +50024,10 @@
       <c r="A254" s="51" t="s">
         <v>203</v>
       </c>
-      <c r="B254" s="59">
+      <c r="B254">
         <v>647831</v>
       </c>
-      <c r="C254" s="59">
+      <c r="C254">
         <v>595177</v>
       </c>
       <c r="D254" s="49">
@@ -50039,10 +50038,10 @@
       <c r="A255" s="51" t="s">
         <v>321</v>
       </c>
-      <c r="B255" s="59">
+      <c r="B255">
         <v>58417</v>
       </c>
-      <c r="C255" s="59">
+      <c r="C255">
         <v>53647</v>
       </c>
       <c r="D255" s="49">
@@ -50053,10 +50052,10 @@
       <c r="A256" s="51" t="s">
         <v>328</v>
       </c>
-      <c r="B256" s="59">
+      <c r="B256">
         <v>620097</v>
       </c>
-      <c r="C256" s="59">
+      <c r="C256">
         <v>569279</v>
       </c>
       <c r="D256" s="49">
@@ -50067,10 +50066,10 @@
       <c r="A257" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="B257" s="59">
+      <c r="B257">
         <v>74841</v>
       </c>
-      <c r="C257" s="59">
+      <c r="C257">
         <v>68688</v>
       </c>
       <c r="D257" s="49">
@@ -50081,10 +50080,10 @@
       <c r="A258" s="51" t="s">
         <v>237</v>
       </c>
-      <c r="B258" s="59">
+      <c r="B258">
         <v>80095</v>
       </c>
-      <c r="C258" s="59">
+      <c r="C258">
         <v>73504</v>
       </c>
       <c r="D258" s="49">
@@ -50095,10 +50094,10 @@
       <c r="A259" s="51" t="s">
         <v>302</v>
       </c>
-      <c r="B259" s="59">
+      <c r="B259">
         <v>132252</v>
       </c>
-      <c r="C259" s="59">
+      <c r="C259">
         <v>121368</v>
       </c>
       <c r="D259" s="49">
@@ -50109,10 +50108,10 @@
       <c r="A260" s="51" t="s">
         <v>304</v>
       </c>
-      <c r="B260" s="59">
+      <c r="B260">
         <v>128290</v>
       </c>
-      <c r="C260" s="59">
+      <c r="C260">
         <v>117718</v>
       </c>
       <c r="D260" s="49">
@@ -50123,10 +50122,10 @@
       <c r="A261" s="51" t="s">
         <v>126</v>
       </c>
-      <c r="B261" s="59">
+      <c r="B261">
         <v>102804</v>
       </c>
-      <c r="C261" s="59">
+      <c r="C261">
         <v>94331</v>
       </c>
       <c r="D261" s="49">
@@ -50137,10 +50136,10 @@
       <c r="A262" s="51" t="s">
         <v>341</v>
       </c>
-      <c r="B262" s="59">
+      <c r="B262">
         <v>169870</v>
       </c>
-      <c r="C262" s="59">
+      <c r="C262">
         <v>155839</v>
       </c>
       <c r="D262" s="49">
@@ -50151,10 +50150,10 @@
       <c r="A263" s="51" t="s">
         <v>245</v>
       </c>
-      <c r="B263" s="59">
+      <c r="B263">
         <v>185584</v>
       </c>
-      <c r="C263" s="59">
+      <c r="C263">
         <v>170239</v>
       </c>
       <c r="D263" s="49">
@@ -50165,10 +50164,10 @@
       <c r="A264" s="51" t="s">
         <v>281</v>
       </c>
-      <c r="B264" s="59">
+      <c r="B264">
         <v>76951</v>
       </c>
-      <c r="C264" s="59">
+      <c r="C264">
         <v>70564</v>
       </c>
       <c r="D264" s="49">
@@ -50179,10 +50178,10 @@
       <c r="A265" s="51" t="s">
         <v>169</v>
       </c>
-      <c r="B265" s="59">
+      <c r="B265">
         <v>154915</v>
       </c>
-      <c r="C265" s="59">
+      <c r="C265">
         <v>141974</v>
       </c>
       <c r="D265" s="49">
@@ -50193,10 +50192,10 @@
       <c r="A266" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="B266" s="59">
+      <c r="B266">
         <v>120008</v>
       </c>
-      <c r="C266" s="59">
+      <c r="C266">
         <v>109948</v>
       </c>
       <c r="D266" s="49">
@@ -50207,10 +50206,10 @@
       <c r="A267" s="51" t="s">
         <v>195</v>
       </c>
-      <c r="B267" s="59">
+      <c r="B267">
         <v>505542</v>
       </c>
-      <c r="C267" s="59">
+      <c r="C267">
         <v>463007</v>
       </c>
       <c r="D267" s="49">
@@ -50221,10 +50220,10 @@
       <c r="A268" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="B268" s="59">
+      <c r="B268">
         <v>187952</v>
       </c>
-      <c r="C268" s="59">
+      <c r="C268">
         <v>172057</v>
       </c>
       <c r="D268" s="49">
@@ -50235,10 +50234,10 @@
       <c r="A269" s="51" t="s">
         <v>279</v>
       </c>
-      <c r="B269" s="59">
+      <c r="B269">
         <v>81424</v>
       </c>
-      <c r="C269" s="59">
+      <c r="C269">
         <v>74535</v>
       </c>
       <c r="D269" s="49">
@@ -50249,10 +50248,10 @@
       <c r="A270" s="51" t="s">
         <v>298</v>
       </c>
-      <c r="B270" s="59">
+      <c r="B270">
         <v>313497</v>
       </c>
-      <c r="C270" s="59">
+      <c r="C270">
         <v>286914</v>
       </c>
       <c r="D270" s="49">
@@ -50263,10 +50262,10 @@
       <c r="A271" s="51" t="s">
         <v>215</v>
       </c>
-      <c r="B271" s="59">
+      <c r="B271">
         <v>104852</v>
       </c>
-      <c r="C271" s="59">
+      <c r="C271">
         <v>95910</v>
       </c>
       <c r="D271" s="49">
@@ -50277,10 +50276,10 @@
       <c r="A272" s="51" t="s">
         <v>286</v>
       </c>
-      <c r="B272" s="59">
+      <c r="B272">
         <v>61610</v>
       </c>
-      <c r="C272" s="59">
+      <c r="C272">
         <v>56346</v>
       </c>
       <c r="D272" s="49">
@@ -50291,10 +50290,10 @@
       <c r="A273" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="B273" s="59">
+      <c r="B273">
         <v>182325</v>
       </c>
-      <c r="C273" s="59">
+      <c r="C273">
         <v>166737</v>
       </c>
       <c r="D273" s="49">
@@ -50305,10 +50304,10 @@
       <c r="A274" s="51" t="s">
         <v>151</v>
       </c>
-      <c r="B274" s="59">
+      <c r="B274">
         <v>60678</v>
       </c>
-      <c r="C274" s="59">
+      <c r="C274">
         <v>55487</v>
       </c>
       <c r="D274" s="49">
@@ -50319,10 +50318,10 @@
       <c r="A275" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="B275" s="59">
+      <c r="B275">
         <v>63223</v>
       </c>
-      <c r="C275" s="59">
+      <c r="C275">
         <v>57775</v>
       </c>
       <c r="D275" s="49">
@@ -50333,10 +50332,10 @@
       <c r="A276" s="51" t="s">
         <v>406</v>
       </c>
-      <c r="B276" s="59">
+      <c r="B276">
         <v>4441248</v>
       </c>
-      <c r="C276" s="59">
+      <c r="C276">
         <v>4058151</v>
       </c>
       <c r="D276" s="49">
@@ -50347,10 +50346,10 @@
       <c r="A277" s="51" t="s">
         <v>315</v>
       </c>
-      <c r="B277" s="59">
+      <c r="B277">
         <v>73342</v>
       </c>
-      <c r="C277" s="59">
+      <c r="C277">
         <v>67002</v>
       </c>
       <c r="D277" s="49">
@@ -50361,10 +50360,10 @@
       <c r="A278" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="B278" s="59">
+      <c r="B278">
         <v>99844</v>
       </c>
-      <c r="C278" s="59">
+      <c r="C278">
         <v>91212</v>
       </c>
       <c r="D278" s="49">
@@ -50375,10 +50374,10 @@
       <c r="A279" s="51" t="s">
         <v>146</v>
       </c>
-      <c r="B279" s="59">
+      <c r="B279">
         <v>69548</v>
       </c>
-      <c r="C279" s="59">
+      <c r="C279">
         <v>63493</v>
       </c>
       <c r="D279" s="49">
@@ -50389,10 +50388,10 @@
       <c r="A280" s="51" t="s">
         <v>148</v>
       </c>
-      <c r="B280" s="59">
+      <c r="B280">
         <v>67754</v>
       </c>
-      <c r="C280" s="59">
+      <c r="C280">
         <v>61816</v>
       </c>
       <c r="D280" s="49">
@@ -50403,10 +50402,10 @@
       <c r="A281" s="51" t="s">
         <v>277</v>
       </c>
-      <c r="B281" s="59">
+      <c r="B281">
         <v>94645</v>
       </c>
-      <c r="C281" s="59">
+      <c r="C281">
         <v>86333</v>
       </c>
       <c r="D281" s="49">
@@ -50417,10 +50416,10 @@
       <c r="A282" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="B282" s="59">
+      <c r="B282">
         <v>121363</v>
       </c>
-      <c r="C282" s="59">
+      <c r="C282">
         <v>110697</v>
       </c>
       <c r="D282" s="49">
@@ -50431,10 +50430,10 @@
       <c r="A283" s="51" t="s">
         <v>262</v>
       </c>
-      <c r="B283" s="59">
+      <c r="B283">
         <v>663096</v>
       </c>
-      <c r="C283" s="59">
+      <c r="C283">
         <v>604468</v>
       </c>
       <c r="D283" s="49">
@@ -50445,10 +50444,10 @@
       <c r="A284" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="B284" s="59">
+      <c r="B284">
         <v>63625</v>
       </c>
-      <c r="C284" s="59">
+      <c r="C284">
         <v>57985</v>
       </c>
       <c r="D284" s="49">
@@ -50459,10 +50458,10 @@
       <c r="A285" s="51" t="s">
         <v>358</v>
       </c>
-      <c r="B285" s="59">
+      <c r="B285">
         <v>54445</v>
       </c>
-      <c r="C285" s="59">
+      <c r="C285">
         <v>49618</v>
       </c>
       <c r="D285" s="49">
@@ -50473,10 +50472,10 @@
       <c r="A286" s="51" t="s">
         <v>261</v>
       </c>
-      <c r="B286" s="59">
+      <c r="B286">
         <v>985408</v>
       </c>
-      <c r="C286" s="59">
+      <c r="C286">
         <v>897973</v>
       </c>
       <c r="D286" s="49">
@@ -50487,10 +50486,10 @@
       <c r="A287" s="51" t="s">
         <v>316</v>
       </c>
-      <c r="B287" s="59">
+      <c r="B287">
         <v>69984</v>
       </c>
-      <c r="C287" s="59">
+      <c r="C287">
         <v>63760</v>
       </c>
       <c r="D287" s="49">
@@ -50501,10 +50500,10 @@
       <c r="A288" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="B288" s="59">
+      <c r="B288">
         <v>1518951</v>
       </c>
-      <c r="C288" s="59">
+      <c r="C288">
         <v>1382523</v>
       </c>
       <c r="D288" s="49">
@@ -50515,10 +50514,10 @@
       <c r="A289" s="51" t="s">
         <v>201</v>
       </c>
-      <c r="B289" s="59">
+      <c r="B289">
         <v>52635</v>
       </c>
-      <c r="C289" s="59">
+      <c r="C289">
         <v>47842</v>
       </c>
       <c r="D289" s="49">
@@ -50529,10 +50528,10 @@
       <c r="A290" s="51" t="s">
         <v>336</v>
       </c>
-      <c r="B290" s="59">
+      <c r="B290">
         <v>241228</v>
       </c>
-      <c r="C290" s="59">
+      <c r="C290">
         <v>219240</v>
       </c>
       <c r="D290" s="49">
@@ -50543,10 +50542,10 @@
       <c r="A291" s="51" t="s">
         <v>125</v>
       </c>
-      <c r="B291" s="59">
+      <c r="B291">
         <v>116008</v>
       </c>
-      <c r="C291" s="59">
+      <c r="C291">
         <v>105326</v>
       </c>
       <c r="D291" s="49">
@@ -50557,10 +50556,10 @@
       <c r="A292" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="B292" s="59">
+      <c r="B292">
         <v>88290</v>
       </c>
-      <c r="C292" s="59">
+      <c r="C292">
         <v>80153</v>
       </c>
       <c r="D292" s="49">
@@ -50571,10 +50570,10 @@
       <c r="A293" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="B293" s="59">
+      <c r="B293">
         <v>466432</v>
       </c>
-      <c r="C293" s="59">
+      <c r="C293">
         <v>423378</v>
       </c>
       <c r="D293" s="49">
@@ -50585,10 +50584,10 @@
       <c r="A294" s="51" t="s">
         <v>140</v>
       </c>
-      <c r="B294" s="59">
+      <c r="B294">
         <v>83475</v>
       </c>
-      <c r="C294" s="59">
+      <c r="C294">
         <v>75746</v>
       </c>
       <c r="D294" s="49">
@@ -50599,10 +50598,10 @@
       <c r="A295" s="51" t="s">
         <v>128</v>
       </c>
-      <c r="B295" s="59">
+      <c r="B295">
         <v>101620</v>
       </c>
-      <c r="C295" s="59">
+      <c r="C295">
         <v>92181</v>
       </c>
       <c r="D295" s="49">
@@ -50613,10 +50612,10 @@
       <c r="A296" s="51" t="s">
         <v>145</v>
       </c>
-      <c r="B296" s="59">
+      <c r="B296">
         <v>69788</v>
       </c>
-      <c r="C296" s="59">
+      <c r="C296">
         <v>63290</v>
       </c>
       <c r="D296" s="49">
@@ -50627,10 +50626,10 @@
       <c r="A297" s="51" t="s">
         <v>309</v>
       </c>
-      <c r="B297" s="59">
+      <c r="B297">
         <v>98214</v>
       </c>
-      <c r="C297" s="59">
+      <c r="C297">
         <v>89065</v>
       </c>
       <c r="D297" s="49">
@@ -50641,10 +50640,10 @@
       <c r="A298" s="51" t="s">
         <v>153</v>
       </c>
-      <c r="B298" s="59">
+      <c r="B298">
         <v>60126</v>
       </c>
-      <c r="C298" s="59">
+      <c r="C298">
         <v>54525</v>
       </c>
       <c r="D298" s="49">
@@ -50655,10 +50654,10 @@
       <c r="A299" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="B299" s="59">
+      <c r="B299">
         <v>92407</v>
       </c>
-      <c r="C299" s="59">
+      <c r="C299">
         <v>83745</v>
       </c>
       <c r="D299" s="49">
@@ -50669,10 +50668,10 @@
       <c r="A300" s="51" t="s">
         <v>236</v>
       </c>
-      <c r="B300" s="59">
+      <c r="B300">
         <v>97665</v>
       </c>
-      <c r="C300" s="59">
+      <c r="C300">
         <v>88474</v>
       </c>
       <c r="D300" s="49">
@@ -50683,10 +50682,10 @@
       <c r="A301" s="51" t="s">
         <v>182</v>
       </c>
-      <c r="B301" s="59">
+      <c r="B301">
         <v>62361</v>
       </c>
-      <c r="C301" s="59">
+      <c r="C301">
         <v>56459</v>
       </c>
       <c r="D301" s="49">
@@ -50697,10 +50696,10 @@
       <c r="A302" s="51" t="s">
         <v>124</v>
       </c>
-      <c r="B302" s="59">
+      <c r="B302">
         <v>123549</v>
       </c>
-      <c r="C302" s="59">
+      <c r="C302">
         <v>111761</v>
       </c>
       <c r="D302" s="49">
@@ -50711,10 +50710,10 @@
       <c r="A303" s="51" t="s">
         <v>189</v>
       </c>
-      <c r="B303" s="59">
+      <c r="B303">
         <v>53307</v>
       </c>
-      <c r="C303" s="59">
+      <c r="C303">
         <v>48213</v>
       </c>
       <c r="D303" s="49">
@@ -50725,10 +50724,10 @@
       <c r="A304" s="51" t="s">
         <v>241</v>
       </c>
-      <c r="B304" s="59">
+      <c r="B304">
         <v>62394</v>
       </c>
-      <c r="C304" s="59">
+      <c r="C304">
         <v>56428</v>
       </c>
       <c r="D304" s="49">
@@ -50739,10 +50738,10 @@
       <c r="A305" s="51" t="s">
         <v>190</v>
       </c>
-      <c r="B305" s="59">
+      <c r="B305">
         <v>65017</v>
       </c>
-      <c r="C305" s="59">
+      <c r="C305">
         <v>58760</v>
       </c>
       <c r="D305" s="49">
@@ -50753,10 +50752,10 @@
       <c r="A306" s="51" t="s">
         <v>150</v>
       </c>
-      <c r="B306" s="59">
+      <c r="B306">
         <v>61062</v>
       </c>
-      <c r="C306" s="59">
+      <c r="C306">
         <v>55149</v>
       </c>
       <c r="D306" s="49">
@@ -50767,10 +50766,10 @@
       <c r="A307" s="51" t="s">
         <v>216</v>
       </c>
-      <c r="B307" s="59">
+      <c r="B307">
         <v>104966</v>
       </c>
-      <c r="C307" s="59">
+      <c r="C307">
         <v>94792</v>
       </c>
       <c r="D307" s="49">
@@ -50781,10 +50780,10 @@
       <c r="A308" s="51" t="s">
         <v>284</v>
       </c>
-      <c r="B308" s="59">
+      <c r="B308">
         <v>67566</v>
       </c>
-      <c r="C308" s="59">
+      <c r="C308">
         <v>61009</v>
       </c>
       <c r="D308" s="49">
@@ -50795,10 +50794,10 @@
       <c r="A309" s="51" t="s">
         <v>301</v>
       </c>
-      <c r="B309" s="59">
+      <c r="B309">
         <v>148588</v>
       </c>
-      <c r="C309" s="59">
+      <c r="C309">
         <v>134165</v>
       </c>
       <c r="D309" s="49">
@@ -50809,10 +50808,10 @@
       <c r="A310" s="51" t="s">
         <v>180</v>
       </c>
-      <c r="B310" s="59">
+      <c r="B310">
         <v>70670</v>
       </c>
-      <c r="C310" s="59">
+      <c r="C310">
         <v>63788</v>
       </c>
       <c r="D310" s="49">
@@ -50823,10 +50822,10 @@
       <c r="A311" s="51" t="s">
         <v>265</v>
       </c>
-      <c r="B311" s="59">
+      <c r="B311">
         <v>194659</v>
       </c>
-      <c r="C311" s="59">
+      <c r="C311">
         <v>175637</v>
       </c>
       <c r="D311" s="49">
@@ -50837,10 +50836,10 @@
       <c r="A312" s="51" t="s">
         <v>296</v>
       </c>
-      <c r="B312" s="59">
+      <c r="B312">
         <v>731209</v>
       </c>
-      <c r="C312" s="59">
+      <c r="C312">
         <v>659724</v>
       </c>
       <c r="D312" s="49">
@@ -50851,10 +50850,10 @@
       <c r="A313" s="51" t="s">
         <v>152</v>
       </c>
-      <c r="B313" s="59">
+      <c r="B313">
         <v>60656</v>
       </c>
-      <c r="C313" s="59">
+      <c r="C313">
         <v>54725</v>
       </c>
       <c r="D313" s="49">
@@ -50865,10 +50864,10 @@
       <c r="A314" s="51" t="s">
         <v>149</v>
       </c>
-      <c r="B314" s="59">
+      <c r="B314">
         <v>63689</v>
       </c>
-      <c r="C314" s="59">
+      <c r="C314">
         <v>57447</v>
       </c>
       <c r="D314" s="49">
@@ -50879,10 +50878,10 @@
       <c r="A315" s="51" t="s">
         <v>319</v>
       </c>
-      <c r="B315" s="59">
+      <c r="B315">
         <v>62331</v>
       </c>
-      <c r="C315" s="59">
+      <c r="C315">
         <v>56219</v>
       </c>
       <c r="D315" s="49">
@@ -50893,10 +50892,10 @@
       <c r="A316" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="B316" s="59">
+      <c r="B316">
         <v>84145</v>
       </c>
-      <c r="C316" s="59">
+      <c r="C316">
         <v>75764</v>
       </c>
       <c r="D316" s="49">
@@ -50907,10 +50906,10 @@
       <c r="A317" s="51" t="s">
         <v>71</v>
       </c>
-      <c r="B317" s="59">
+      <c r="B317">
         <v>340894</v>
       </c>
-      <c r="C317" s="59">
+      <c r="C317">
         <v>306910</v>
       </c>
       <c r="D317" s="49">
@@ -50921,10 +50920,10 @@
       <c r="A318" s="51" t="s">
         <v>244</v>
       </c>
-      <c r="B318" s="59">
+      <c r="B318">
         <v>291027</v>
       </c>
-      <c r="C318" s="59">
+      <c r="C318">
         <v>261943</v>
       </c>
       <c r="D318" s="49">
@@ -50935,10 +50934,10 @@
       <c r="A319" s="51" t="s">
         <v>184</v>
       </c>
-      <c r="B319" s="59">
+      <c r="B319">
         <v>58228</v>
       </c>
-      <c r="C319" s="59">
+      <c r="C319">
         <v>52380</v>
       </c>
       <c r="D319" s="49">
@@ -50949,10 +50948,10 @@
       <c r="A320" s="51" t="s">
         <v>134</v>
       </c>
-      <c r="B320" s="59">
+      <c r="B320">
         <v>94080</v>
       </c>
-      <c r="C320" s="59">
+      <c r="C320">
         <v>84601</v>
       </c>
       <c r="D320" s="49">
@@ -50963,10 +50962,10 @@
       <c r="A321" s="51" t="s">
         <v>324</v>
       </c>
-      <c r="B321" s="59">
+      <c r="B321">
         <v>2659484</v>
       </c>
-      <c r="C321" s="59">
+      <c r="C321">
         <v>2390484</v>
       </c>
       <c r="D321" s="49">
@@ -50977,10 +50976,10 @@
       <c r="A322" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="B322" s="59">
+      <c r="B322">
         <v>99129</v>
       </c>
-      <c r="C322" s="59">
+      <c r="C322">
         <v>89101</v>
       </c>
       <c r="D322" s="49">
@@ -50991,10 +50990,10 @@
       <c r="A323" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="B323" s="59">
+      <c r="B323">
         <v>599332</v>
       </c>
-      <c r="C323" s="59">
+      <c r="C323">
         <v>538483</v>
       </c>
       <c r="D323" s="49">
@@ -51005,10 +51004,10 @@
       <c r="A324" s="51" t="s">
         <v>291</v>
       </c>
-      <c r="B324" s="59">
+      <c r="B324">
         <v>52931</v>
       </c>
-      <c r="C324" s="59">
+      <c r="C324">
         <v>47535</v>
       </c>
       <c r="D324" s="49">
@@ -51019,10 +51018,10 @@
       <c r="A325" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="B325" s="59">
+      <c r="B325">
         <v>1619280</v>
       </c>
-      <c r="C325" s="59">
+      <c r="C325">
         <v>1454070</v>
       </c>
       <c r="D325" s="49">
@@ -51033,10 +51032,10 @@
       <c r="A326" s="51" t="s">
         <v>141</v>
       </c>
-      <c r="B326" s="59">
+      <c r="B326">
         <v>81524</v>
       </c>
-      <c r="C326" s="59">
+      <c r="C326">
         <v>73168</v>
       </c>
       <c r="D326" s="49">
@@ -51047,10 +51046,10 @@
       <c r="A327" s="51" t="s">
         <v>177</v>
       </c>
-      <c r="B327" s="59">
+      <c r="B327">
         <v>77687</v>
       </c>
-      <c r="C327" s="59">
+      <c r="C327">
         <v>69709</v>
       </c>
       <c r="D327" s="49">
@@ -51061,10 +51060,10 @@
       <c r="A328" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="B328" s="59">
+      <c r="B328">
         <v>62171</v>
       </c>
-      <c r="C328" s="59">
+      <c r="C328">
         <v>55783</v>
       </c>
       <c r="D328" s="49">
@@ -51075,10 +51074,10 @@
       <c r="A329" s="51" t="s">
         <v>293</v>
       </c>
-      <c r="B329" s="59">
+      <c r="B329">
         <v>3348264</v>
       </c>
-      <c r="C329" s="59">
+      <c r="C329">
         <v>3003990</v>
       </c>
       <c r="D329" s="49">
@@ -51089,10 +51088,10 @@
       <c r="A330" s="51" t="s">
         <v>168</v>
       </c>
-      <c r="B330" s="59">
+      <c r="B330">
         <v>161346</v>
       </c>
-      <c r="C330" s="59">
+      <c r="C330">
         <v>144743</v>
       </c>
       <c r="D330" s="49">
@@ -51103,10 +51102,10 @@
       <c r="A331" s="51" t="s">
         <v>240</v>
       </c>
-      <c r="B331" s="59">
+      <c r="B331">
         <v>63244</v>
       </c>
-      <c r="C331" s="59">
+      <c r="C331">
         <v>56728</v>
       </c>
       <c r="D331" s="49">
@@ -51117,10 +51116,10 @@
       <c r="A332" s="51" t="s">
         <v>154</v>
       </c>
-      <c r="B332" s="59">
+      <c r="B332">
         <v>60238</v>
       </c>
-      <c r="C332" s="59">
+      <c r="C332">
         <v>54016</v>
       </c>
       <c r="D332" s="49">
@@ -51131,10 +51130,10 @@
       <c r="A333" s="51" t="s">
         <v>172</v>
       </c>
-      <c r="B333" s="59">
+      <c r="B333">
         <v>126834</v>
       </c>
-      <c r="C333" s="59">
+      <c r="C333">
         <v>113731</v>
       </c>
       <c r="D333" s="49">
@@ -51145,10 +51144,10 @@
       <c r="A334" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="B334" s="59">
+      <c r="B334">
         <v>112280</v>
       </c>
-      <c r="C334" s="59">
+      <c r="C334">
         <v>100675</v>
       </c>
       <c r="D334" s="49">
@@ -51159,10 +51158,10 @@
       <c r="A335" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="B335" s="59">
+      <c r="B335">
         <v>365148</v>
       </c>
-      <c r="C335" s="59">
+      <c r="C335">
         <v>327371</v>
       </c>
       <c r="D335" s="49">
@@ -51173,10 +51172,10 @@
       <c r="A336" s="51" t="s">
         <v>167</v>
       </c>
-      <c r="B336" s="59">
+      <c r="B336">
         <v>163892</v>
       </c>
-      <c r="C336" s="59">
+      <c r="C336">
         <v>146925</v>
       </c>
       <c r="D336" s="49">
@@ -51187,10 +51186,10 @@
       <c r="A337" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="B337" s="59">
+      <c r="B337">
         <v>83536</v>
       </c>
-      <c r="C337" s="59">
+      <c r="C337">
         <v>74868</v>
       </c>
       <c r="D337" s="49">
@@ -51201,10 +51200,10 @@
       <c r="A338" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="B338" s="59">
+      <c r="B338">
         <v>72311</v>
       </c>
-      <c r="C338" s="59">
+      <c r="C338">
         <v>64757</v>
       </c>
       <c r="D338" s="49">
@@ -51215,10 +51214,10 @@
       <c r="A339" s="51" t="s">
         <v>135</v>
       </c>
-      <c r="B339" s="59">
+      <c r="B339">
         <v>88704</v>
       </c>
-      <c r="C339" s="59">
+      <c r="C339">
         <v>79424</v>
       </c>
       <c r="D339" s="49">
@@ -51229,10 +51228,10 @@
       <c r="A340" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="B340" s="59">
+      <c r="B340">
         <v>71401</v>
       </c>
-      <c r="C340" s="59">
+      <c r="C340">
         <v>63929</v>
       </c>
       <c r="D340" s="49">
@@ -51243,10 +51242,10 @@
       <c r="A341" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="B341" s="59">
+      <c r="B341">
         <v>103533</v>
       </c>
-      <c r="C341" s="59">
+      <c r="C341">
         <v>92683</v>
       </c>
       <c r="D341" s="49">
@@ -51257,10 +51256,10 @@
       <c r="A342" s="51" t="s">
         <v>326</v>
       </c>
-      <c r="B342" s="59">
+      <c r="B342">
         <v>824641</v>
       </c>
-      <c r="C342" s="59">
+      <c r="C342">
         <v>738128</v>
       </c>
       <c r="D342" s="49">
@@ -51271,10 +51270,10 @@
       <c r="A343" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="B343" s="59">
+      <c r="B343">
         <v>81527</v>
       </c>
-      <c r="C343" s="59">
+      <c r="C343">
         <v>72958</v>
       </c>
       <c r="D343" s="49">
@@ -51285,10 +51284,10 @@
       <c r="A344" s="51" t="s">
         <v>85</v>
       </c>
-      <c r="B344" s="59">
+      <c r="B344">
         <v>68643</v>
       </c>
-      <c r="C344" s="59">
+      <c r="C344">
         <v>61387</v>
       </c>
       <c r="D344" s="49">
@@ -51299,10 +51298,10 @@
       <c r="A345" s="51" t="s">
         <v>139</v>
       </c>
-      <c r="B345" s="59">
+      <c r="B345">
         <v>84546</v>
       </c>
-      <c r="C345" s="59">
+      <c r="C345">
         <v>75600</v>
       </c>
       <c r="D345" s="49">
@@ -51313,10 +51312,10 @@
       <c r="A346" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="B346" s="59">
+      <c r="B346">
         <v>377174</v>
       </c>
-      <c r="C346" s="59">
+      <c r="C346">
         <v>337049</v>
       </c>
       <c r="D346" s="49">
@@ -51327,10 +51326,10 @@
       <c r="A347" s="51" t="s">
         <v>267</v>
       </c>
-      <c r="B347" s="59">
+      <c r="B347">
         <v>149460</v>
       </c>
-      <c r="C347" s="59">
+      <c r="C347">
         <v>133544</v>
       </c>
       <c r="D347" s="49">
@@ -51341,10 +51340,10 @@
       <c r="A348" s="51" t="s">
         <v>114</v>
       </c>
-      <c r="B348" s="59">
+      <c r="B348">
         <v>261338</v>
       </c>
-      <c r="C348" s="59">
+      <c r="C348">
         <v>233454</v>
       </c>
       <c r="D348" s="49">
@@ -51355,10 +51354,10 @@
       <c r="A349" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="B349" s="59">
+      <c r="B349">
         <v>96806</v>
       </c>
-      <c r="C349" s="59">
+      <c r="C349">
         <v>86476</v>
       </c>
       <c r="D349" s="49">
@@ -51369,10 +51368,10 @@
       <c r="A350" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="B350" s="59">
+      <c r="B350">
         <v>79817</v>
       </c>
-      <c r="C350" s="59">
+      <c r="C350">
         <v>71287</v>
       </c>
       <c r="D350" s="49">
@@ -51383,10 +51382,10 @@
       <c r="A351" s="51" t="s">
         <v>322</v>
       </c>
-      <c r="B351" s="59">
+      <c r="B351">
         <v>58724</v>
       </c>
-      <c r="C351" s="59">
+      <c r="C351">
         <v>52425</v>
       </c>
       <c r="D351" s="49">
@@ -51397,10 +51396,10 @@
       <c r="A352" s="51" t="s">
         <v>308</v>
       </c>
-      <c r="B352" s="59">
+      <c r="B352">
         <v>100495</v>
       </c>
-      <c r="C352" s="59">
+      <c r="C352">
         <v>89694</v>
       </c>
       <c r="D352" s="49">
@@ -51411,10 +51410,10 @@
       <c r="A353" s="51" t="s">
         <v>143</v>
       </c>
-      <c r="B353" s="59">
+      <c r="B353">
         <v>75384</v>
       </c>
-      <c r="C353" s="59">
+      <c r="C353">
         <v>67252</v>
       </c>
       <c r="D353" s="49">
@@ -51425,10 +51424,10 @@
       <c r="A354" s="51" t="s">
         <v>162</v>
       </c>
-      <c r="B354" s="59">
+      <c r="B354">
         <v>53507</v>
       </c>
-      <c r="C354" s="59">
+      <c r="C354">
         <v>47734</v>
       </c>
       <c r="D354" s="49">
@@ -51439,10 +51438,10 @@
       <c r="A355" s="51" t="s">
         <v>280</v>
       </c>
-      <c r="B355" s="59">
+      <c r="B355">
         <v>78070</v>
       </c>
-      <c r="C355" s="59">
+      <c r="C355">
         <v>69618</v>
       </c>
       <c r="D355" s="49">
@@ -51453,10 +51452,10 @@
       <c r="A356" s="51" t="s">
         <v>108</v>
       </c>
-      <c r="B356" s="59">
+      <c r="B356">
         <v>371858</v>
       </c>
-      <c r="C356" s="59">
+      <c r="C356">
         <v>331487</v>
       </c>
       <c r="D356" s="49">
@@ -51467,10 +51466,10 @@
       <c r="A357" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="B357" s="59">
+      <c r="B357">
         <v>104201</v>
       </c>
-      <c r="C357" s="59">
+      <c r="C357">
         <v>92845</v>
       </c>
       <c r="D357" s="49">
@@ -51481,10 +51480,10 @@
       <c r="A358" s="51" t="s">
         <v>122</v>
       </c>
-      <c r="B358" s="59">
+      <c r="B358">
         <v>135829</v>
       </c>
-      <c r="C358" s="59">
+      <c r="C358">
         <v>120961</v>
       </c>
       <c r="D358" s="49">
@@ -51495,10 +51494,10 @@
       <c r="A359" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="B359" s="59">
+      <c r="B359">
         <v>183087</v>
       </c>
-      <c r="C359" s="59">
+      <c r="C359">
         <v>163016</v>
       </c>
       <c r="D359" s="49">
@@ -51509,10 +51508,10 @@
       <c r="A360" s="51" t="s">
         <v>132</v>
       </c>
-      <c r="B360" s="59">
+      <c r="B360">
         <v>98529</v>
       </c>
-      <c r="C360" s="59">
+      <c r="C360">
         <v>87712</v>
       </c>
       <c r="D360" s="49">
@@ -51523,10 +51522,10 @@
       <c r="A361" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="B361" s="59">
+      <c r="B361">
         <v>76840</v>
       </c>
-      <c r="C361" s="59">
+      <c r="C361">
         <v>68398</v>
       </c>
       <c r="D361" s="49">
@@ -51537,10 +51536,10 @@
       <c r="A362" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="B362" s="59">
+      <c r="B362">
         <v>529795</v>
       </c>
-      <c r="C362" s="59">
+      <c r="C362">
         <v>471570</v>
       </c>
       <c r="D362" s="49">
@@ -51551,10 +51550,10 @@
       <c r="A363" s="51" t="s">
         <v>278</v>
       </c>
-      <c r="B363" s="59">
+      <c r="B363">
         <v>95227</v>
       </c>
-      <c r="C363" s="59">
+      <c r="C363">
         <v>84745</v>
       </c>
       <c r="D363" s="49">
@@ -51565,10 +51564,10 @@
       <c r="A364" s="51" t="s">
         <v>175</v>
       </c>
-      <c r="B364" s="59">
+      <c r="B364">
         <v>82663</v>
       </c>
-      <c r="C364" s="59">
+      <c r="C364">
         <v>73537</v>
       </c>
       <c r="D364" s="49">
@@ -51579,10 +51578,10 @@
       <c r="A365" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="B365" s="59">
+      <c r="B365">
         <v>67811</v>
       </c>
-      <c r="C365" s="59">
+      <c r="C365">
         <v>60319</v>
       </c>
       <c r="D365" s="49">
@@ -51593,10 +51592,10 @@
       <c r="A366" s="51" t="s">
         <v>486</v>
       </c>
-      <c r="B366" s="59">
+      <c r="B366">
         <v>53247</v>
       </c>
-      <c r="C366" s="59">
+      <c r="C366">
         <v>47361</v>
       </c>
       <c r="D366" s="49">
@@ -51607,10 +51606,10 @@
       <c r="A367" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="B367" s="59">
+      <c r="B367">
         <v>180680</v>
       </c>
-      <c r="C367" s="59">
+      <c r="C367">
         <v>160703</v>
       </c>
       <c r="D367" s="49">
@@ -51621,10 +51620,10 @@
       <c r="A368" s="51" t="s">
         <v>269</v>
       </c>
-      <c r="B368" s="59">
+      <c r="B368">
         <v>124634</v>
       </c>
-      <c r="C368" s="59">
+      <c r="C368">
         <v>110788</v>
       </c>
       <c r="D368" s="49">
@@ -51635,10 +51634,10 @@
       <c r="A369" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="B369" s="59">
+      <c r="B369">
         <v>160659</v>
       </c>
-      <c r="C369" s="59">
+      <c r="C369">
         <v>142766</v>
       </c>
       <c r="D369" s="49">
@@ -51649,10 +51648,10 @@
       <c r="A370" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="B370" s="59">
+      <c r="B370">
         <v>62005</v>
       </c>
-      <c r="C370" s="59">
+      <c r="C370">
         <v>55080</v>
       </c>
       <c r="D370" s="49">
@@ -51663,10 +51662,10 @@
       <c r="A371" s="51" t="s">
         <v>166</v>
       </c>
-      <c r="B371" s="59">
+      <c r="B371">
         <v>208509</v>
       </c>
-      <c r="C371" s="59">
+      <c r="C371">
         <v>185215</v>
       </c>
       <c r="D371" s="49">
@@ -51677,10 +51676,10 @@
       <c r="A372" s="51" t="s">
         <v>142</v>
       </c>
-      <c r="B372" s="59">
+      <c r="B372">
         <v>77766</v>
       </c>
-      <c r="C372" s="59">
+      <c r="C372">
         <v>69065</v>
       </c>
       <c r="D372" s="49">
@@ -51691,10 +51690,10 @@
       <c r="A373" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="B373" s="59">
+      <c r="B373">
         <v>754857</v>
       </c>
-      <c r="C373" s="59">
+      <c r="C373">
         <v>670051</v>
       </c>
       <c r="D373" s="49">
@@ -51705,10 +51704,10 @@
       <c r="A374" s="51" t="s">
         <v>232</v>
       </c>
-      <c r="B374" s="59">
+      <c r="B374">
         <v>633363</v>
       </c>
-      <c r="C374" s="59">
+      <c r="C374">
         <v>561935</v>
       </c>
       <c r="D374" s="49">
@@ -51719,10 +51718,10 @@
       <c r="A375" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="B375" s="59">
+      <c r="B375">
         <v>197754</v>
       </c>
-      <c r="C375" s="59">
+      <c r="C375">
         <v>175379</v>
       </c>
       <c r="D375" s="49">
@@ -51733,10 +51732,10 @@
       <c r="A376" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="B376" s="59">
+      <c r="B376">
         <v>76657</v>
       </c>
-      <c r="C376" s="59">
+      <c r="C376">
         <v>67976</v>
       </c>
       <c r="D376" s="49">
@@ -51747,10 +51746,10 @@
       <c r="A377" s="51" t="s">
         <v>147</v>
       </c>
-      <c r="B377" s="59">
+      <c r="B377">
         <v>69446</v>
       </c>
-      <c r="C377" s="59">
+      <c r="C377">
         <v>61577</v>
       </c>
       <c r="D377" s="49">
@@ -51761,10 +51760,10 @@
       <c r="A378" s="51" t="s">
         <v>434</v>
       </c>
-      <c r="B378" s="59">
+      <c r="B378">
         <v>53585</v>
       </c>
-      <c r="C378" s="59">
+      <c r="C378">
         <v>47483</v>
       </c>
       <c r="D378" s="49">
@@ -51775,10 +51774,10 @@
       <c r="A379" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="B379" s="59">
+      <c r="B379">
         <v>74689</v>
       </c>
-      <c r="C379" s="59">
+      <c r="C379">
         <v>66175</v>
       </c>
       <c r="D379" s="49">
@@ -51789,10 +51788,10 @@
       <c r="A380" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="B380" s="59">
+      <c r="B380">
         <v>761060</v>
       </c>
-      <c r="C380" s="59">
+      <c r="C380">
         <v>674053</v>
       </c>
       <c r="D380" s="49">
@@ -51803,10 +51802,10 @@
       <c r="A381" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="B381" s="59">
+      <c r="B381">
         <v>84808</v>
       </c>
-      <c r="C381" s="59">
+      <c r="C381">
         <v>75089</v>
       </c>
       <c r="D381" s="49">
@@ -51817,10 +51816,10 @@
       <c r="A382" s="51" t="s">
         <v>183</v>
       </c>
-      <c r="B382" s="59">
+      <c r="B382">
         <v>59946</v>
       </c>
-      <c r="C382" s="59">
+      <c r="C382">
         <v>53066</v>
       </c>
       <c r="D382" s="49">
@@ -51831,10 +51830,10 @@
       <c r="A383" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="B383" s="59">
+      <c r="B383">
         <v>58401</v>
       </c>
-      <c r="C383" s="59">
+      <c r="C383">
         <v>51690</v>
       </c>
       <c r="D383" s="49">
@@ -51845,10 +51844,10 @@
       <c r="A384" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="B384" s="59">
+      <c r="B384">
         <v>69560</v>
       </c>
-      <c r="C384" s="59">
+      <c r="C384">
         <v>61561</v>
       </c>
       <c r="D384" s="49">
@@ -51859,10 +51858,10 @@
       <c r="A385" s="51" t="s">
         <v>164</v>
       </c>
-      <c r="B385" s="59">
+      <c r="B385">
         <v>249797</v>
       </c>
-      <c r="C385" s="59">
+      <c r="C385">
         <v>221042</v>
       </c>
       <c r="D385" s="49">
@@ -51873,10 +51872,10 @@
       <c r="A386" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="B386" s="59">
+      <c r="B386">
         <v>236238</v>
       </c>
-      <c r="C386" s="59">
+      <c r="C386">
         <v>208958</v>
       </c>
       <c r="D386" s="49">
@@ -51887,10 +51886,10 @@
       <c r="A387" s="51" t="s">
         <v>161</v>
       </c>
-      <c r="B387" s="59">
+      <c r="B387">
         <v>54521</v>
       </c>
-      <c r="C387" s="59">
+      <c r="C387">
         <v>48212</v>
       </c>
       <c r="D387" s="49">
@@ -51901,10 +51900,10 @@
       <c r="A388" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="B388" s="59">
+      <c r="B388">
         <v>482828</v>
       </c>
-      <c r="C388" s="59">
+      <c r="C388">
         <v>426731</v>
       </c>
       <c r="D388" s="49">
@@ -51915,10 +51914,10 @@
       <c r="A389" s="51" t="s">
         <v>242</v>
       </c>
-      <c r="B389" s="59">
+      <c r="B389">
         <v>468302</v>
       </c>
-      <c r="C389" s="59">
+      <c r="C389">
         <v>413686</v>
       </c>
       <c r="D389" s="49">
@@ -51929,10 +51928,10 @@
       <c r="A390" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="B390" s="59">
+      <c r="B390">
         <v>463975</v>
       </c>
-      <c r="C390" s="59">
+      <c r="C390">
         <v>409750</v>
       </c>
       <c r="D390" s="49">
@@ -51943,10 +51942,10 @@
       <c r="A391" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="B391" s="59">
+      <c r="B391">
         <v>151782</v>
       </c>
-      <c r="C391" s="59">
+      <c r="C391">
         <v>134031</v>
       </c>
       <c r="D391" s="49">
@@ -51957,10 +51956,10 @@
       <c r="A392" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="B392" s="59">
+      <c r="B392">
         <v>113173</v>
       </c>
-      <c r="C392" s="59">
+      <c r="C392">
         <v>99928</v>
       </c>
       <c r="D392" s="49">
@@ -51971,10 +51970,10 @@
       <c r="A393" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="B393" s="59">
+      <c r="B393">
         <v>111622</v>
       </c>
-      <c r="C393" s="59">
+      <c r="C393">
         <v>98553</v>
       </c>
       <c r="D393" s="49">
@@ -51985,10 +51984,10 @@
       <c r="A394" s="51" t="s">
         <v>234</v>
       </c>
-      <c r="B394" s="59">
+      <c r="B394">
         <v>299232</v>
       </c>
-      <c r="C394" s="59">
+      <c r="C394">
         <v>264185</v>
       </c>
       <c r="D394" s="49">
@@ -51999,10 +51998,10 @@
       <c r="A395" s="51" t="s">
         <v>159</v>
       </c>
-      <c r="B395" s="59">
+      <c r="B395">
         <v>57017</v>
       </c>
-      <c r="C395" s="59">
+      <c r="C395">
         <v>50283</v>
       </c>
       <c r="D395" s="49">
@@ -52013,10 +52012,10 @@
       <c r="A396" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="B396" s="59">
+      <c r="B396">
         <v>1087864</v>
       </c>
-      <c r="C396" s="59">
+      <c r="C396">
         <v>958788</v>
       </c>
       <c r="D396" s="49">
@@ -52027,10 +52026,10 @@
       <c r="A397" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="B397" s="59">
+      <c r="B397">
         <v>56178</v>
       </c>
-      <c r="C397" s="59">
+      <c r="C397">
         <v>49512</v>
       </c>
       <c r="D397" s="49">
@@ -52041,10 +52040,10 @@
       <c r="A398" s="51" t="s">
         <v>120</v>
       </c>
-      <c r="B398" s="59">
+      <c r="B398">
         <v>139694</v>
       </c>
-      <c r="C398" s="59">
+      <c r="C398">
         <v>123107</v>
       </c>
       <c r="D398" s="49">
@@ -52055,10 +52054,10 @@
       <c r="A399" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="B399" s="59">
+      <c r="B399">
         <v>134348</v>
       </c>
-      <c r="C399" s="59">
+      <c r="C399">
         <v>118258</v>
       </c>
       <c r="D399" s="49">
@@ -52069,10 +52068,10 @@
       <c r="A400" s="51" t="s">
         <v>327</v>
       </c>
-      <c r="B400" s="59">
+      <c r="B400">
         <v>649535</v>
       </c>
-      <c r="C400" s="59">
+      <c r="C400">
         <v>571698</v>
       </c>
       <c r="D400" s="49">
@@ -52083,10 +52082,10 @@
       <c r="A401" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="B401" s="59">
+      <c r="B401">
         <v>677260</v>
       </c>
-      <c r="C401" s="59">
+      <c r="C401">
         <v>596052</v>
       </c>
       <c r="D401" s="49">
@@ -52097,10 +52096,10 @@
       <c r="A402" s="51" t="s">
         <v>130</v>
       </c>
-      <c r="B402" s="59">
+      <c r="B402">
         <v>101434</v>
       </c>
-      <c r="C402" s="59">
+      <c r="C402">
         <v>89191</v>
       </c>
       <c r="D402" s="49">
@@ -52111,10 +52110,10 @@
       <c r="A403" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="B403" s="59">
+      <c r="B403">
         <v>218284</v>
       </c>
-      <c r="C403" s="59">
+      <c r="C403">
         <v>191926</v>
       </c>
       <c r="D403" s="49">
@@ -52125,10 +52124,10 @@
       <c r="A404" s="51" t="s">
         <v>118</v>
       </c>
-      <c r="B404" s="59">
+      <c r="B404">
         <v>154630</v>
       </c>
-      <c r="C404" s="59">
+      <c r="C404">
         <v>135910</v>
       </c>
       <c r="D404" s="49">
@@ -52139,10 +52138,10 @@
       <c r="A405" s="51" t="s">
         <v>176</v>
       </c>
-      <c r="B405" s="59">
+      <c r="B405">
         <v>82589</v>
       </c>
-      <c r="C405" s="59">
+      <c r="C405">
         <v>72586</v>
       </c>
       <c r="D405" s="49">
@@ -52153,10 +52152,10 @@
       <c r="A406" s="51" t="s">
         <v>303</v>
       </c>
-      <c r="B406" s="59">
+      <c r="B406">
         <v>132388</v>
       </c>
-      <c r="C406" s="59">
+      <c r="C406">
         <v>116317</v>
       </c>
       <c r="D406" s="49">
@@ -52167,10 +52166,10 @@
       <c r="A407" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="B407" s="59">
+      <c r="B407">
         <v>630114</v>
       </c>
-      <c r="C407" s="59">
+      <c r="C407">
         <v>553591</v>
       </c>
       <c r="D407" s="49">
@@ -52181,10 +52180,10 @@
       <c r="A408" s="51" t="s">
         <v>271</v>
       </c>
-      <c r="B408" s="59">
+      <c r="B408">
         <v>117276</v>
       </c>
-      <c r="C408" s="59">
+      <c r="C408">
         <v>103019</v>
       </c>
       <c r="D408" s="49">
@@ -52195,10 +52194,10 @@
       <c r="A409" s="51" t="s">
         <v>113</v>
       </c>
-      <c r="B409" s="59">
+      <c r="B409">
         <v>292497</v>
       </c>
-      <c r="C409" s="59">
+      <c r="C409">
         <v>256894</v>
       </c>
       <c r="D409" s="49">
@@ -52209,10 +52208,10 @@
       <c r="A410" s="51" t="s">
         <v>133</v>
       </c>
-      <c r="B410" s="59">
+      <c r="B410">
         <v>97335</v>
       </c>
-      <c r="C410" s="59">
+      <c r="C410">
         <v>85476</v>
       </c>
       <c r="D410" s="49">
@@ -52223,10 +52222,10 @@
       <c r="A411" s="51" t="s">
         <v>112</v>
       </c>
-      <c r="B411" s="59">
+      <c r="B411">
         <v>321624</v>
       </c>
-      <c r="C411" s="59">
+      <c r="C411">
         <v>282173</v>
       </c>
       <c r="D411" s="49">
@@ -52237,10 +52236,10 @@
       <c r="A412" s="51" t="s">
         <v>138</v>
       </c>
-      <c r="B412" s="59">
+      <c r="B412">
         <v>85473</v>
       </c>
-      <c r="C412" s="59">
+      <c r="C412">
         <v>74959</v>
       </c>
       <c r="D412" s="49">
@@ -52251,10 +52250,10 @@
       <c r="A413" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="B413" s="59">
+      <c r="B413">
         <v>88561</v>
       </c>
-      <c r="C413" s="59">
+      <c r="C413">
         <v>77664</v>
       </c>
       <c r="D413" s="49">
@@ -52265,10 +52264,10 @@
       <c r="A414" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="B414" s="59">
+      <c r="B414">
         <v>1256783</v>
       </c>
-      <c r="C414" s="59">
+      <c r="C414">
         <v>1101742</v>
       </c>
       <c r="D414" s="49">
@@ -52279,10 +52278,10 @@
       <c r="A415" s="51" t="s">
         <v>235</v>
       </c>
-      <c r="B415" s="59">
+      <c r="B415">
         <v>108243</v>
       </c>
-      <c r="C415" s="59">
+      <c r="C415">
         <v>94873</v>
       </c>
       <c r="D415" s="49">
@@ -52293,10 +52292,10 @@
       <c r="A416" s="51" t="s">
         <v>136</v>
       </c>
-      <c r="B416" s="59">
+      <c r="B416">
         <v>87908</v>
       </c>
-      <c r="C416" s="59">
+      <c r="C416">
         <v>77017</v>
       </c>
       <c r="D416" s="49">
@@ -52307,10 +52306,10 @@
       <c r="A417" s="51" t="s">
         <v>105</v>
       </c>
-      <c r="B417" s="59">
+      <c r="B417">
         <v>522385</v>
       </c>
-      <c r="C417" s="59">
+      <c r="C417">
         <v>457548</v>
       </c>
       <c r="D417" s="49">
@@ -52321,10 +52320,10 @@
       <c r="A418" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="B418" s="59">
+      <c r="B418">
         <v>105372</v>
       </c>
-      <c r="C418" s="59">
+      <c r="C418">
         <v>92290</v>
       </c>
       <c r="D418" s="49">
@@ -52335,10 +52334,10 @@
       <c r="A419" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="B419" s="59">
+      <c r="B419">
         <v>54466</v>
       </c>
-      <c r="C419" s="59">
+      <c r="C419">
         <v>47692</v>
       </c>
       <c r="D419" s="49">
@@ -52349,10 +52348,10 @@
       <c r="A420" s="51" t="s">
         <v>156</v>
       </c>
-      <c r="B420" s="59">
+      <c r="B420">
         <v>59340</v>
       </c>
-      <c r="C420" s="59">
+      <c r="C420">
         <v>51947</v>
       </c>
       <c r="D420" s="49">
@@ -52363,10 +52362,10 @@
       <c r="A421" s="51" t="s">
         <v>171</v>
       </c>
-      <c r="B421" s="59">
+      <c r="B421">
         <v>133931</v>
       </c>
-      <c r="C421" s="59">
+      <c r="C421">
         <v>117205</v>
       </c>
       <c r="D421" s="49">
@@ -52377,10 +52376,10 @@
       <c r="A422" s="51" t="s">
         <v>137</v>
       </c>
-      <c r="B422" s="59">
+      <c r="B422">
         <v>86028</v>
       </c>
-      <c r="C422" s="59">
+      <c r="C422">
         <v>75261</v>
       </c>
       <c r="D422" s="49">
@@ -52391,10 +52390,10 @@
       <c r="A423" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="B423" s="59">
+      <c r="B423">
         <v>165667</v>
       </c>
-      <c r="C423" s="59">
+      <c r="C423">
         <v>144895</v>
       </c>
       <c r="D423" s="49">
@@ -52405,10 +52404,10 @@
       <c r="A424" s="51" t="s">
         <v>170</v>
       </c>
-      <c r="B424" s="59">
+      <c r="B424">
         <v>139319</v>
       </c>
-      <c r="C424" s="59">
+      <c r="C424">
         <v>121780</v>
       </c>
       <c r="D424" s="49">
@@ -52419,10 +52418,10 @@
       <c r="A425" s="51" t="s">
         <v>186</v>
       </c>
-      <c r="B425" s="59">
+      <c r="B425">
         <v>56526</v>
       </c>
-      <c r="C425" s="59">
+      <c r="C425">
         <v>49398</v>
       </c>
       <c r="D425" s="49">
@@ -52433,10 +52432,10 @@
       <c r="A426" s="51" t="s">
         <v>314</v>
       </c>
-      <c r="B426" s="59">
+      <c r="B426">
         <v>75167</v>
       </c>
-      <c r="C426" s="59">
+      <c r="C426">
         <v>65672</v>
       </c>
       <c r="D426" s="49">
@@ -52447,10 +52446,10 @@
       <c r="A427" s="51" t="s">
         <v>160</v>
       </c>
-      <c r="B427" s="59">
+      <c r="B427">
         <v>57236</v>
       </c>
-      <c r="C427" s="59">
+      <c r="C427">
         <v>49997</v>
       </c>
       <c r="D427" s="49">
@@ -52461,10 +52460,10 @@
       <c r="A428" s="51" t="s">
         <v>200</v>
       </c>
-      <c r="B428" s="59">
+      <c r="B428">
         <v>67063</v>
       </c>
-      <c r="C428" s="59">
+      <c r="C428">
         <v>58574</v>
       </c>
       <c r="D428" s="49">
@@ -52475,10 +52474,10 @@
       <c r="A429" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="B429" s="59">
+      <c r="B429">
         <v>78561</v>
       </c>
-      <c r="C429" s="59">
+      <c r="C429">
         <v>68565</v>
       </c>
       <c r="D429" s="49">
@@ -52489,10 +52488,10 @@
       <c r="A430" s="51" t="s">
         <v>275</v>
       </c>
-      <c r="B430" s="59">
+      <c r="B430">
         <v>105394</v>
       </c>
-      <c r="C430" s="59">
+      <c r="C430">
         <v>91938</v>
       </c>
       <c r="D430" s="49">
@@ -52503,10 +52502,10 @@
       <c r="A431" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="B431" s="59">
+      <c r="B431">
         <v>750446</v>
       </c>
-      <c r="C431" s="59">
+      <c r="C431">
         <v>654207</v>
       </c>
       <c r="D431" s="49">
@@ -52517,10 +52516,10 @@
       <c r="A432" s="51" t="s">
         <v>263</v>
       </c>
-      <c r="B432" s="59">
+      <c r="B432">
         <v>588752</v>
       </c>
-      <c r="C432" s="59">
+      <c r="C432">
         <v>513229</v>
       </c>
       <c r="D432" s="49">
@@ -52531,10 +52530,10 @@
       <c r="A433" s="51" t="s">
         <v>187</v>
       </c>
-      <c r="B433" s="59">
+      <c r="B433">
         <v>56231</v>
       </c>
-      <c r="C433" s="59">
+      <c r="C433">
         <v>48990</v>
       </c>
       <c r="D433" s="49">
@@ -52545,10 +52544,10 @@
       <c r="A434" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="B434" s="59">
+      <c r="B434">
         <v>156246</v>
       </c>
-      <c r="C434" s="59">
+      <c r="C434">
         <v>136093</v>
       </c>
       <c r="D434" s="49">
@@ -52559,10 +52558,10 @@
       <c r="A435" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="B435" s="59">
+      <c r="B435">
         <v>62302</v>
       </c>
-      <c r="C435" s="59">
+      <c r="C435">
         <v>54152</v>
       </c>
       <c r="D435" s="49">
@@ -52573,10 +52572,10 @@
       <c r="A436" s="51" t="s">
         <v>123</v>
       </c>
-      <c r="B436" s="59">
+      <c r="B436">
         <v>131534</v>
       </c>
-      <c r="C436" s="59">
+      <c r="C436">
         <v>114283</v>
       </c>
       <c r="D436" s="49">
@@ -52587,10 +52586,10 @@
       <c r="A437" s="51" t="s">
         <v>239</v>
       </c>
-      <c r="B437" s="59">
+      <c r="B437">
         <v>70879</v>
       </c>
-      <c r="C437" s="59">
+      <c r="C437">
         <v>61562</v>
       </c>
       <c r="D437" s="49">
@@ -52601,10 +52600,10 @@
       <c r="A438" s="51" t="s">
         <v>188</v>
       </c>
-      <c r="B438" s="59">
+      <c r="B438">
         <v>54868</v>
       </c>
-      <c r="C438" s="59">
+      <c r="C438">
         <v>47588</v>
       </c>
       <c r="D438" s="49">
@@ -52615,10 +52614,10 @@
       <c r="A439" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="B439" s="59">
+      <c r="B439">
         <v>8739213</v>
       </c>
-      <c r="C439" s="59">
+      <c r="C439">
         <v>7575625</v>
       </c>
       <c r="D439" s="49">
@@ -52629,10 +52628,10 @@
       <c r="A440" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="B440" s="59">
+      <c r="B440">
         <v>205346</v>
       </c>
-      <c r="C440" s="59">
+      <c r="C440">
         <v>177972</v>
       </c>
       <c r="D440" s="49">
@@ -52643,10 +52642,10 @@
       <c r="A441" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="B441" s="59">
+      <c r="B441">
         <v>237006</v>
       </c>
-      <c r="C441" s="59">
+      <c r="C441">
         <v>205271</v>
       </c>
       <c r="D441" s="49">
@@ -52657,10 +52656,10 @@
       <c r="A442" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="B442" s="59">
+      <c r="B442">
         <v>71481</v>
       </c>
-      <c r="C442" s="59">
+      <c r="C442">
         <v>61748</v>
       </c>
       <c r="D442" s="49">
@@ -52671,10 +52670,10 @@
       <c r="A443" s="51" t="s">
         <v>121</v>
       </c>
-      <c r="B443" s="59">
+      <c r="B443">
         <v>139074</v>
       </c>
-      <c r="C443" s="59">
+      <c r="C443">
         <v>120086</v>
       </c>
       <c r="D443" s="49">
@@ -52685,10 +52684,10 @@
       <c r="A444" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="B444" s="59">
+      <c r="B444">
         <v>350035</v>
       </c>
-      <c r="C444" s="59">
+      <c r="C444">
         <v>301791</v>
       </c>
       <c r="D444" s="49">
@@ -52699,10 +52698,10 @@
       <c r="A445" s="51" t="s">
         <v>115</v>
       </c>
-      <c r="B445" s="59">
+      <c r="B445">
         <v>244333</v>
       </c>
-      <c r="C445" s="59">
+      <c r="C445">
         <v>210604</v>
       </c>
       <c r="D445" s="49">
@@ -52713,10 +52712,10 @@
       <c r="A446" s="51" t="s">
         <v>323</v>
       </c>
-      <c r="B446" s="59">
+      <c r="B446">
         <v>9894088</v>
       </c>
-      <c r="C446" s="59">
+      <c r="C446">
         <v>8520200</v>
       </c>
       <c r="D446" s="49">
@@ -52727,10 +52726,10 @@
       <c r="A447" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="B447" s="59">
+      <c r="B447">
         <v>134435</v>
       </c>
-      <c r="C447" s="59">
+      <c r="C447">
         <v>115606</v>
       </c>
       <c r="D447" s="49">
@@ -52741,10 +52740,10 @@
       <c r="A448" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="B448" s="59">
+      <c r="B448">
         <v>91736</v>
       </c>
-      <c r="C448" s="59">
+      <c r="C448">
         <v>78690</v>
       </c>
       <c r="D448" s="49">
@@ -52755,10 +52754,10 @@
       <c r="A449" s="51" t="s">
         <v>181</v>
       </c>
-      <c r="B449" s="59">
+      <c r="B449">
         <v>67438</v>
       </c>
-      <c r="C449" s="59">
+      <c r="C449">
         <v>57745</v>
       </c>
       <c r="D449" s="49">
@@ -52769,10 +52768,10 @@
       <c r="A450" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="B450" s="59">
+      <c r="B450">
         <v>655734</v>
       </c>
-      <c r="C450" s="59">
+      <c r="C450">
         <v>560985</v>
       </c>
       <c r="D450" s="49">
@@ -52783,10 +52782,10 @@
       <c r="A451" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="B451" s="59">
+      <c r="B451">
         <v>942441</v>
       </c>
-      <c r="C451" s="59">
+      <c r="C451">
         <v>804026</v>
       </c>
       <c r="D451" s="49">
@@ -52797,10 +52796,10 @@
       <c r="A452" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="B452" s="59">
+      <c r="B452">
         <v>83655</v>
       </c>
-      <c r="C452" s="59">
+      <c r="C452">
         <v>71307</v>
       </c>
       <c r="D452" s="49">
@@ -52811,10 +52810,10 @@
       <c r="A453" s="51" t="s">
         <v>207</v>
       </c>
-      <c r="B453" s="59">
+      <c r="B453">
         <v>175073</v>
       </c>
-      <c r="C453" s="59">
+      <c r="C453">
         <v>149164</v>
       </c>
       <c r="D453" s="49">
@@ -52825,10 +52824,10 @@
       <c r="A454" s="51" t="s">
         <v>274</v>
       </c>
-      <c r="B454" s="59">
+      <c r="B454">
         <v>108405</v>
       </c>
-      <c r="C454" s="59">
+      <c r="C454">
         <v>92101</v>
       </c>
       <c r="D454" s="49">
@@ -52839,10 +52838,10 @@
       <c r="A455" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="B455" s="59">
+      <c r="B455">
         <v>148042</v>
       </c>
-      <c r="C455" s="59">
+      <c r="C455">
         <v>125460</v>
       </c>
       <c r="D455" s="49">
@@ -52853,10 +52852,10 @@
       <c r="A456" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="B456" s="59">
+      <c r="B456">
         <v>488808</v>
       </c>
-      <c r="C456" s="59">
+      <c r="C456">
         <v>413160</v>
       </c>
       <c r="D456" s="49">
@@ -52867,10 +52866,10 @@
       <c r="A457" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="B457" s="59">
+      <c r="B457">
         <v>874773</v>
       </c>
-      <c r="C457" s="59">
+      <c r="C457">
         <v>739105</v>
       </c>
       <c r="D457" s="49">
@@ -52881,10 +52880,10 @@
       <c r="A458" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="B458" s="59">
+      <c r="B458">
         <v>112840</v>
       </c>
-      <c r="C458" s="59">
+      <c r="C458">
         <v>95094</v>
       </c>
       <c r="D458" s="49">
@@ -52895,10 +52894,10 @@
       <c r="A459" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="B459" s="59">
+      <c r="B459">
         <v>1584967</v>
       </c>
-      <c r="C459" s="59">
+      <c r="C459">
         <v>1335100</v>
       </c>
       <c r="D459" s="49">
@@ -52909,10 +52908,10 @@
       <c r="A460" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="B460" s="59">
+      <c r="B460">
         <v>166623</v>
       </c>
-      <c r="C460" s="59">
+      <c r="C460">
         <v>140270</v>
       </c>
       <c r="D460" s="49">
@@ -52923,10 +52922,10 @@
       <c r="A461" s="51" t="s">
         <v>158</v>
       </c>
-      <c r="B461" s="59">
+      <c r="B461">
         <v>58662</v>
       </c>
-      <c r="C461" s="59">
+      <c r="C461">
         <v>49014</v>
       </c>
       <c r="D461" s="49">
@@ -52937,10 +52936,10 @@
       <c r="A462" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="B462" s="59">
+      <c r="B462">
         <v>55485</v>
       </c>
-      <c r="C462" s="59">
+      <c r="C462">
         <v>46169</v>
       </c>
       <c r="D462" s="49">
@@ -52951,10 +52950,10 @@
       <c r="A463" s="51" t="s">
         <v>110</v>
       </c>
-      <c r="B463" s="59">
+      <c r="B463">
         <v>352577</v>
       </c>
-      <c r="C463" s="59">
+      <c r="C463">
         <v>289804</v>
       </c>
       <c r="D463" s="49">
@@ -52965,10 +52964,10 @@
       <c r="A464" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="B464" s="59">
+      <c r="B464">
         <v>563127</v>
       </c>
-      <c r="C464" s="59">
+      <c r="C464">
         <v>462555</v>
       </c>
       <c r="D464" s="49">
@@ -52979,10 +52978,10 @@
       <c r="A465" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="B465" s="59">
+      <c r="B465">
         <v>94797</v>
       </c>
-      <c r="C465" s="59">
+      <c r="C465">
         <v>77020</v>
       </c>
       <c r="D465" s="49">
@@ -52993,10 +52992,10 @@
       <c r="A466" s="51" t="s">
         <v>346</v>
       </c>
-      <c r="B466" s="59">
+      <c r="B466">
         <v>107771</v>
       </c>
-      <c r="C466" s="59">
+      <c r="C466">
         <v>87228</v>
       </c>
       <c r="D466" s="49">
@@ -53007,10 +53006,10 @@
       <c r="A467" s="51" t="s">
         <v>285</v>
       </c>
-      <c r="B467" s="59">
+      <c r="B467">
         <v>70577</v>
       </c>
-      <c r="C467" s="59">
+      <c r="C467">
         <v>55522</v>
       </c>
       <c r="D467" s="49">
@@ -53021,10 +53020,10 @@
       <c r="A468" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="B468" s="59">
+      <c r="B468">
         <v>59757</v>
       </c>
-      <c r="C468" s="59">
+      <c r="C468">
         <v>45126</v>
       </c>
       <c r="D468" s="49">
@@ -53035,10 +53034,10 @@
       <c r="A469" s="51" t="s">
         <v>294</v>
       </c>
-      <c r="B469" s="59">
+      <c r="B469">
         <v>2613841</v>
       </c>
-      <c r="C469" s="59">
+      <c r="C469">
         <v>1971526</v>
       </c>
       <c r="D469" s="49">
@@ -53049,10 +53048,10 @@
       <c r="A470" s="51" t="s">
         <v>312</v>
       </c>
-      <c r="B470" s="59">
+      <c r="B470">
         <v>94338</v>
       </c>
-      <c r="C470" s="59">
+      <c r="C470">
         <v>69267</v>
       </c>
       <c r="D470" s="49">
@@ -53063,10 +53062,10 @@
       <c r="A471" s="51" t="s">
         <v>330</v>
       </c>
-      <c r="B471" s="59">
+      <c r="B471">
         <v>434975</v>
       </c>
-      <c r="C471" s="59">
+      <c r="C471">
         <v>302436</v>
       </c>
       <c r="D471" s="49">
@@ -53077,10 +53076,10 @@
       <c r="A472" s="51" t="s">
         <v>493</v>
       </c>
-      <c r="B472" s="59">
+      <c r="B472">
         <v>137877283</v>
       </c>
-      <c r="C472" s="59">
+      <c r="C472">
         <v>127014230</v>
       </c>
       <c r="D472" s="49">
@@ -53117,41 +53116,41 @@
   <sheetData>
     <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:9" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="53" t="s">
+      <c r="A11" s="55" t="s">
         <v>489</v>
       </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="55"/>
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="57"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="56" t="s">
+      <c r="A14" s="58" t="s">
         <v>490</v>
       </c>
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="56"/>
-      <c r="H14" s="56"/>
-      <c r="I14" s="56"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="58"/>
+      <c r="I14" s="58"/>
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="56"/>
-      <c r="B15" s="56"/>
-      <c r="C15" s="56"/>
-      <c r="D15" s="56"/>
-      <c r="E15" s="56"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="56"/>
-      <c r="H15" s="56"/>
-      <c r="I15" s="56"/>
+      <c r="A15" s="58"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="58"/>
+      <c r="I15" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="2">
